--- a/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F914"/>
+  <dimension ref="A1:F948"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -604,7 +604,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %; nunca 0,04 num campo sem formato). Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
         </is>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].nome (tipo = cronograma)</t>
+          <t>fases[1].nome</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].inicio_mes</t>
+          <t>fases[1].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].duracao_meses</t>
+          <t>fases[1].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].nome (tipo = cronograma)</t>
+          <t>fases[2].nome</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].inicio_mes</t>
+          <t>fases[2].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].duracao_meses</t>
+          <t>fases[2].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].nome (tipo = cronograma)</t>
+          <t>fases[3].nome</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].inicio_mes</t>
+          <t>fases[3].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].duracao_meses</t>
+          <t>fases[3].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].nome (tipo = cronograma)</t>
+          <t>fases[4].nome</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].inicio_mes</t>
+          <t>fases[4].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1472,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].duracao_meses</t>
+          <t>fases[4].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].nome (tipo = cronograma)</t>
+          <t>fases[5].nome</t>
         </is>
       </c>
     </row>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].inicio_mes</t>
+          <t>fases[5].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].duracao_meses</t>
+          <t>fases[5].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].nome</t>
+          <t>tipologias[1].nome</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].tipo_unidade</t>
+          <t>tipologias[1].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].area_privativa_m2</t>
+          <t>tipologias[1].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].area_privativa_aberta_m2</t>
+          <t>tipologias[1].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].dormitorios</t>
+          <t>tipologias[1].dormitorios</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].vagas</t>
+          <t>tipologias[1].vagas</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].quantidade</t>
+          <t>tipologias[1].quantidade</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[1].preco_m2</t>
+          <t>tipologias[1].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].nome</t>
+          <t>tipologias[2].nome</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].tipo_unidade</t>
+          <t>tipologias[2].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].area_privativa_m2</t>
+          <t>tipologias[2].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].area_privativa_aberta_m2</t>
+          <t>tipologias[2].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].dormitorios</t>
+          <t>tipologias[2].dormitorios</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].vagas</t>
+          <t>tipologias[2].vagas</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].quantidade</t>
+          <t>tipologias[2].quantidade</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[2].preco_m2</t>
+          <t>tipologias[2].preco_m2</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].nome</t>
+          <t>tipologias[3].nome</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].tipo_unidade</t>
+          <t>tipologias[3].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].area_privativa_m2</t>
+          <t>tipologias[3].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].area_privativa_aberta_m2</t>
+          <t>tipologias[3].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].dormitorios</t>
+          <t>tipologias[3].dormitorios</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].vagas</t>
+          <t>tipologias[3].vagas</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].quantidade</t>
+          <t>tipologias[3].quantidade</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[3].preco_m2</t>
+          <t>tipologias[3].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].nome</t>
+          <t>tipologias[4].nome</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].tipo_unidade</t>
+          <t>tipologias[4].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].area_privativa_m2</t>
+          <t>tipologias[4].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].area_privativa_aberta_m2</t>
+          <t>tipologias[4].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].dormitorios</t>
+          <t>tipologias[4].dormitorios</t>
         </is>
       </c>
     </row>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].vagas</t>
+          <t>tipologias[4].vagas</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].quantidade</t>
+          <t>tipologias[4].quantidade</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[4].preco_m2</t>
+          <t>tipologias[4].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].nome</t>
+          <t>tipologias[5].nome</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].tipo_unidade</t>
+          <t>tipologias[5].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].area_privativa_m2</t>
+          <t>tipologias[5].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].area_privativa_aberta_m2</t>
+          <t>tipologias[5].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].dormitorios</t>
+          <t>tipologias[5].dormitorios</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].vagas</t>
+          <t>tipologias[5].vagas</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].quantidade</t>
+          <t>tipologias[5].quantidade</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[5].preco_m2</t>
+          <t>tipologias[5].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].nome</t>
+          <t>tipologias[6].nome</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].tipo_unidade</t>
+          <t>tipologias[6].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].area_privativa_m2</t>
+          <t>tipologias[6].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].area_privativa_aberta_m2</t>
+          <t>tipologias[6].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].dormitorios</t>
+          <t>tipologias[6].dormitorios</t>
         </is>
       </c>
     </row>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].vagas</t>
+          <t>tipologias[6].vagas</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].quantidade</t>
+          <t>tipologias[6].quantidade</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[6].preco_m2</t>
+          <t>tipologias[6].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].nome</t>
+          <t>tipologias[7].nome</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].tipo_unidade</t>
+          <t>tipologias[7].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].area_privativa_m2</t>
+          <t>tipologias[7].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].area_privativa_aberta_m2</t>
+          <t>tipologias[7].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].dormitorios</t>
+          <t>tipologias[7].dormitorios</t>
         </is>
       </c>
     </row>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].vagas</t>
+          <t>tipologias[7].vagas</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].quantidade</t>
+          <t>tipologias[7].quantidade</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[7].preco_m2</t>
+          <t>tipologias[7].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].nome</t>
+          <t>tipologias[8].nome</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].tipo_unidade</t>
+          <t>tipologias[8].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].area_privativa_m2</t>
+          <t>tipologias[8].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].area_privativa_aberta_m2</t>
+          <t>tipologias[8].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].dormitorios</t>
+          <t>tipologias[8].dormitorios</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].vagas</t>
+          <t>tipologias[8].vagas</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].quantidade</t>
+          <t>tipologias[8].quantidade</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[8].preco_m2</t>
+          <t>tipologias[8].preco_m2</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].nome</t>
+          <t>tipologias[9].nome</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].tipo_unidade</t>
+          <t>tipologias[9].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].area_privativa_m2</t>
+          <t>tipologias[9].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].area_privativa_aberta_m2</t>
+          <t>tipologias[9].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].dormitorios</t>
+          <t>tipologias[9].dormitorios</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].vagas</t>
+          <t>tipologias[9].vagas</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].quantidade</t>
+          <t>tipologias[9].quantidade</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[9].preco_m2</t>
+          <t>tipologias[9].preco_m2</t>
         </is>
       </c>
     </row>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].nome</t>
+          <t>tipologias[10].nome</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].tipo_unidade</t>
+          <t>tipologias[10].tipo_unidade</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].area_privativa_m2</t>
+          <t>tipologias[10].area_privativa_m2</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].area_privativa_aberta_m2</t>
+          <t>tipologias[10].area_privativa_aberta_m2</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].dormitorios</t>
+          <t>tipologias[10].dormitorios</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].vagas</t>
+          <t>tipologias[10].vagas</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].quantidade</t>
+          <t>tipologias[10].quantidade</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>avancado_tipologias[10].preco_m2</t>
+          <t>tipologias[10].preco_m2</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[1].nome (tipo = receita)</t>
+          <t>grupos[1].nome</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[1].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[1].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[1].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[1].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[1].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[1].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[2].nome (tipo = receita)</t>
+          <t>grupos[2].nome</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[2].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[2].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[2].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[2].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[2].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[2].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[3].nome (tipo = receita)</t>
+          <t>grupos[3].nome</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[3].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[3].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[3].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[3].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[3].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[3].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[4].nome (tipo = receita)</t>
+          <t>grupos[4].nome</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[4].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[4].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[4].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[4].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[4].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[4].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>avancado_fases[5].nome (tipo = receita)</t>
+          <t>grupos[5].nome</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[pre_lancamento].pct</t>
+          <t>grupos[5].pre_lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[lancamento].pct</t>
+          <t>grupos[5].lancamento_pct</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>absorcao.blocos[obra].pct</t>
+          <t>grupos[5].obra_pct</t>
         </is>
       </c>
     </row>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>absorcao.pos_chaves_meses</t>
+          <t>grupos[5].pos_chaves_meses</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>absorcao.correcao_estoque</t>
+          <t>grupos[5].correcao_estoque</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento.residuoAteMarco</t>
+          <t>grupos[5].residuo_sem_prazo</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3966,7 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[1].grupo</t>
+          <t>pagamento[1].grupo</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #1</t>
+          <t>pagamento[1].linha</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>pct #1</t>
+          <t>pagamento[1].pct</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>parcelas #1</t>
+          <t>pagamento[1].parcelas</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #1</t>
+          <t>pagamento[1].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4066,7 @@
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #1</t>
+          <t>pagamento[1].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #1</t>
+          <t>pagamento[1].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[2].grupo</t>
+          <t>pagamento[2].grupo</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #2</t>
+          <t>pagamento[2].linha</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>pct #2</t>
+          <t>pagamento[2].pct</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>parcelas #2</t>
+          <t>pagamento[2].parcelas</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #2</t>
+          <t>pagamento[2].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #2</t>
+          <t>pagamento[2].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4233,7 +4233,7 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #2</t>
+          <t>pagamento[2].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[3].grupo</t>
+          <t>pagamento[3].grupo</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #3</t>
+          <t>pagamento[3].linha</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4304,7 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>pct #3</t>
+          <t>pagamento[3].pct</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>parcelas #3</t>
+          <t>pagamento[3].parcelas</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #3</t>
+          <t>pagamento[3].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #3</t>
+          <t>pagamento[3].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #3</t>
+          <t>pagamento[3].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[4].grupo</t>
+          <t>pagamento[4].grupo</t>
         </is>
       </c>
     </row>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #4</t>
+          <t>pagamento[4].linha</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>pct #4</t>
+          <t>pagamento[4].pct</t>
         </is>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>parcelas #4</t>
+          <t>pagamento[4].parcelas</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #4</t>
+          <t>pagamento[4].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #4</t>
+          <t>pagamento[4].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #4</t>
+          <t>pagamento[4].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4560,7 +4560,7 @@
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[5].grupo</t>
+          <t>pagamento[5].grupo</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #5</t>
+          <t>pagamento[5].linha</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>pct #5</t>
+          <t>pagamento[5].pct</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>parcelas #5</t>
+          <t>pagamento[5].parcelas</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #5</t>
+          <t>pagamento[5].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #5</t>
+          <t>pagamento[5].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #5</t>
+          <t>pagamento[5].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[6].grupo</t>
+          <t>pagamento[6].grupo</t>
         </is>
       </c>
     </row>
@@ -4723,7 +4723,7 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #6</t>
+          <t>pagamento[6].linha</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>pct #6</t>
+          <t>pagamento[6].pct</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>parcelas #6</t>
+          <t>pagamento[6].parcelas</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #6</t>
+          <t>pagamento[6].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #6</t>
+          <t>pagamento[6].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #6</t>
+          <t>pagamento[6].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[7].grupo</t>
+          <t>pagamento[7].grupo</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #7</t>
+          <t>pagamento[7].linha</t>
         </is>
       </c>
     </row>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>pct #7</t>
+          <t>pagamento[7].pct</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>parcelas #7</t>
+          <t>pagamento[7].parcelas</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #7</t>
+          <t>pagamento[7].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #7</t>
+          <t>pagamento[7].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #7</t>
+          <t>pagamento[7].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[8].grupo</t>
+          <t>pagamento[8].grupo</t>
         </is>
       </c>
     </row>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #8</t>
+          <t>pagamento[8].linha</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>pct #8</t>
+          <t>pagamento[8].pct</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>parcelas #8</t>
+          <t>pagamento[8].parcelas</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #8</t>
+          <t>pagamento[8].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #8</t>
+          <t>pagamento[8].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #8</t>
+          <t>pagamento[8].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[9].grupo</t>
+          <t>pagamento[9].grupo</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #9</t>
+          <t>pagamento[9].linha</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>pct #9</t>
+          <t>pagamento[9].pct</t>
         </is>
       </c>
     </row>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>parcelas #9</t>
+          <t>pagamento[9].parcelas</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #9</t>
+          <t>pagamento[9].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #9</t>
+          <t>pagamento[9].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #9</t>
+          <t>pagamento[9].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>fluxo_pagamento[10].grupo</t>
+          <t>pagamento[10].grupo</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>entrada[i] / parcelas[i] #10</t>
+          <t>pagamento[10].linha</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>pct #10</t>
+          <t>pagamento[10].pct</t>
         </is>
       </c>
     </row>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>parcelas #10</t>
+          <t>pagamento[10].parcelas</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>entrada[i].descontoPct #10</t>
+          <t>pagamento[10].desconto_pct</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].sinalPct #10</t>
+          <t>pagamento[10].sinal_pct</t>
         </is>
       </c>
     </row>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>parcelas[i].ao_longo_obra #10</t>
+          <t>pagamento[10].ao_longo_obra</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].fase_id</t>
+          <t>alocacoes[1].grupo</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].tipologia_id</t>
+          <t>alocacoes[1].tipologia</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].unidades</t>
+          <t>alocacoes[1].unidades</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>alocacao[1].preco_m2</t>
+          <t>alocacoes[1].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].fase_id</t>
+          <t>alocacoes[2].grupo</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].tipologia_id</t>
+          <t>alocacoes[2].tipologia</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].unidades</t>
+          <t>alocacoes[2].unidades</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>alocacao[2].preco_m2</t>
+          <t>alocacoes[2].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].fase_id</t>
+          <t>alocacoes[3].grupo</t>
         </is>
       </c>
     </row>
@@ -5585,7 +5585,7 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].tipologia_id</t>
+          <t>alocacoes[3].tipologia</t>
         </is>
       </c>
     </row>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].unidades</t>
+          <t>alocacoes[3].unidades</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>alocacao[3].preco_m2</t>
+          <t>alocacoes[3].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].fase_id</t>
+          <t>alocacoes[4].grupo</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].tipologia_id</t>
+          <t>alocacoes[4].tipologia</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].unidades</t>
+          <t>alocacoes[4].unidades</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>alocacao[4].preco_m2</t>
+          <t>alocacoes[4].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].fase_id</t>
+          <t>alocacoes[5].grupo</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].tipologia_id</t>
+          <t>alocacoes[5].tipologia</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].unidades</t>
+          <t>alocacoes[5].unidades</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>alocacao[5].preco_m2</t>
+          <t>alocacoes[5].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].fase_id</t>
+          <t>alocacoes[6].grupo</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].tipologia_id</t>
+          <t>alocacoes[6].tipologia</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].unidades</t>
+          <t>alocacoes[6].unidades</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>alocacao[6].preco_m2</t>
+          <t>alocacoes[6].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].fase_id</t>
+          <t>alocacoes[7].grupo</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].tipologia_id</t>
+          <t>alocacoes[7].tipologia</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].unidades</t>
+          <t>alocacoes[7].unidades</t>
         </is>
       </c>
     </row>
@@ -5965,7 +5965,7 @@
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>alocacao[7].preco_m2</t>
+          <t>alocacoes[7].preco_m2</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].fase_id</t>
+          <t>alocacoes[8].grupo</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].tipologia_id</t>
+          <t>alocacoes[8].tipologia</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D311" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].unidades</t>
+          <t>alocacoes[8].unidades</t>
         </is>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>alocacao[8].preco_m2</t>
+          <t>alocacoes[8].preco_m2</t>
         </is>
       </c>
     </row>
@@ -6069,7 +6069,7 @@
       </c>
       <c r="D314" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].fase_id</t>
+          <t>alocacoes[9].grupo</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6087,7 @@
       </c>
       <c r="D315" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].tipologia_id</t>
+          <t>alocacoes[9].tipologia</t>
         </is>
       </c>
     </row>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].unidades</t>
+          <t>alocacoes[9].unidades</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6123,7 @@
       </c>
       <c r="D317" s="8" t="inlineStr">
         <is>
-          <t>alocacao[9].preco_m2</t>
+          <t>alocacoes[9].preco_m2</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="D319" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].fase_id</t>
+          <t>alocacoes[10].grupo</t>
         </is>
       </c>
     </row>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].tipologia_id</t>
+          <t>alocacoes[10].tipologia</t>
         </is>
       </c>
     </row>
@@ -6184,7 +6184,7 @@
       </c>
       <c r="D321" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].unidades</t>
+          <t>alocacoes[10].unidades</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>alocacao[10].preco_m2</t>
+          <t>alocacoes[10].preco_m2</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="D327" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].grupo</t>
+          <t>custos[1].grupo</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="D328" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].categoria</t>
+          <t>custos[1].categoria</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="D329" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].subcategoria</t>
+          <t>custos[1].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6318,7 @@
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_unidade</t>
+          <t>custos[1].unidade</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6337,7 @@
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[1].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6354,7 @@
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[1].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].curva_id / distribuicao_modo</t>
+          <t>custos[1].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].cronograma_evento / fase_ancora_id</t>
+          <t>custos[1].cronograma</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].inicio_mes</t>
+          <t>custos[1].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[1].duracao_meses</t>
+          <t>custos[1].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D338" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].grupo</t>
+          <t>custos[2].grupo</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="D339" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].categoria</t>
+          <t>custos[2].categoria</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6507,7 @@
       </c>
       <c r="D340" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].subcategoria</t>
+          <t>custos[2].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="D341" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_unidade</t>
+          <t>custos[2].unidade</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="D342" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[2].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D343" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[2].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="C344" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D344" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].curva_id / distribuicao_modo</t>
+          <t>custos[2].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6609,7 +6609,7 @@
       </c>
       <c r="D345" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].cronograma_evento / fase_ancora_id</t>
+          <t>custos[2].cronograma</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="D346" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].inicio_mes</t>
+          <t>custos[2].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="D347" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[2].duracao_meses</t>
+          <t>custos[2].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D349" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].grupo</t>
+          <t>custos[3].grupo</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="D350" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].categoria</t>
+          <t>custos[3].categoria</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6714,7 @@
       </c>
       <c r="D351" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].subcategoria</t>
+          <t>custos[3].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="D352" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_unidade</t>
+          <t>custos[3].unidade</t>
         </is>
       </c>
     </row>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="D353" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[3].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6772,7 +6772,7 @@
       </c>
       <c r="D354" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[3].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6785,12 +6785,12 @@
       <c r="B355" s="6" t="n"/>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D355" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].curva_id / distribuicao_modo</t>
+          <t>custos[3].distribuicao</t>
         </is>
       </c>
     </row>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D356" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].cronograma_evento / fase_ancora_id</t>
+          <t>custos[3].cronograma</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="D357" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].inicio_mes</t>
+          <t>custos[3].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
       </c>
       <c r="D358" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[3].duracao_meses</t>
+          <t>custos[3].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D360" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].grupo</t>
+          <t>custos[4].grupo</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="D361" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].categoria</t>
+          <t>custos[4].categoria</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6913,7 @@
       </c>
       <c r="D362" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].subcategoria</t>
+          <t>custos[4].subcategoria</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="D363" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_unidade</t>
+          <t>custos[4].unidade</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="D364" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[4].valor_rs</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="D365" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[4].valor_pct</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D366" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].curva_id / distribuicao_modo</t>
+          <t>custos[4].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="D367" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].cronograma_evento / fase_ancora_id</t>
+          <t>custos[4].cronograma</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="D368" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].inicio_mes</t>
+          <t>custos[4].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D369" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[4].duracao_meses</t>
+          <t>custos[4].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="D371" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].grupo</t>
+          <t>custos[5].grupo</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="D372" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].categoria</t>
+          <t>custos[5].categoria</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="D373" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].subcategoria</t>
+          <t>custos[5].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="D374" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_unidade</t>
+          <t>custos[5].unidade</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="D375" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[5].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D376" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[5].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7199,12 +7199,12 @@
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D377" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].curva_id / distribuicao_modo</t>
+          <t>custos[5].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="D378" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].cronograma_evento / fase_ancora_id</t>
+          <t>custos[5].cronograma</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
       </c>
       <c r="D379" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].inicio_mes</t>
+          <t>custos[5].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="D380" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[5].duracao_meses</t>
+          <t>custos[5].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="D382" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].grupo</t>
+          <t>custos[6].grupo</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="D383" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].categoria</t>
+          <t>custos[6].categoria</t>
         </is>
       </c>
     </row>
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D384" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].subcategoria</t>
+          <t>custos[6].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7357,7 @@
       </c>
       <c r="D385" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_unidade</t>
+          <t>custos[6].unidade</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="D386" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[6].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="D387" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[6].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7410,12 +7410,12 @@
       </c>
       <c r="C388" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D388" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].curva_id / distribuicao_modo</t>
+          <t>custos[6].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7437,7 +7437,7 @@
       </c>
       <c r="D389" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].cronograma_evento / fase_ancora_id</t>
+          <t>custos[6].cronograma</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="D390" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].inicio_mes</t>
+          <t>custos[6].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="D391" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[6].duracao_meses</t>
+          <t>custos[6].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="D393" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].grupo</t>
+          <t>custos[7].grupo</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="D394" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].categoria</t>
+          <t>custos[7].categoria</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="D395" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].subcategoria</t>
+          <t>custos[7].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7568,7 +7568,7 @@
       </c>
       <c r="D396" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_unidade</t>
+          <t>custos[7].unidade</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="D397" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[7].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7604,7 @@
       </c>
       <c r="D398" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[7].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7621,12 +7621,12 @@
       </c>
       <c r="C399" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D399" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].curva_id / distribuicao_modo</t>
+          <t>custos[7].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="D400" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].cronograma_evento / fase_ancora_id</t>
+          <t>custos[7].cronograma</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="D401" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].inicio_mes</t>
+          <t>custos[7].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="D402" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[7].duracao_meses</t>
+          <t>custos[7].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7713,7 +7713,7 @@
       </c>
       <c r="D404" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].grupo</t>
+          <t>custos[8].grupo</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="D405" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].categoria</t>
+          <t>custos[8].categoria</t>
         </is>
       </c>
     </row>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="D406" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].subcategoria</t>
+          <t>custos[8].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="D407" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_unidade</t>
+          <t>custos[8].unidade</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="D408" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[8].valor_rs</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D409" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[8].valor_pct</t>
         </is>
       </c>
     </row>
@@ -7828,12 +7828,12 @@
       </c>
       <c r="C410" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D410" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].curva_id / distribuicao_modo</t>
+          <t>custos[8].distribuicao</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="D411" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].cronograma_evento / fase_ancora_id</t>
+          <t>custos[8].cronograma</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="D412" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].inicio_mes</t>
+          <t>custos[8].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -7891,7 +7891,7 @@
       </c>
       <c r="D413" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[8].duracao_meses</t>
+          <t>custos[8].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="D415" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].grupo</t>
+          <t>custos[9].grupo</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="D416" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].categoria</t>
+          <t>custos[9].categoria</t>
         </is>
       </c>
     </row>
@@ -7960,7 +7960,7 @@
       </c>
       <c r="D417" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].subcategoria</t>
+          <t>custos[9].subcategoria</t>
         </is>
       </c>
     </row>
@@ -7982,7 +7982,7 @@
       </c>
       <c r="D418" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_unidade</t>
+          <t>custos[9].unidade</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="D419" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[9].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D420" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[9].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8035,12 +8035,12 @@
       </c>
       <c r="C421" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D421" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].curva_id / distribuicao_modo</t>
+          <t>custos[9].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8062,7 +8062,7 @@
       </c>
       <c r="D422" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].cronograma_evento / fase_ancora_id</t>
+          <t>custos[9].cronograma</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D423" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].inicio_mes</t>
+          <t>custos[9].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="D424" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[9].duracao_meses</t>
+          <t>custos[9].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="D426" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].grupo</t>
+          <t>custos[10].grupo</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="D427" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].categoria</t>
+          <t>custos[10].categoria</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="D428" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].subcategoria</t>
+          <t>custos[10].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="D429" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_unidade</t>
+          <t>custos[10].unidade</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="D430" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[10].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8225,7 @@
       </c>
       <c r="D431" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[10].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="C432" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D432" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].curva_id / distribuicao_modo</t>
+          <t>custos[10].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="D433" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].cronograma_evento / fase_ancora_id</t>
+          <t>custos[10].cronograma</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="D434" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].inicio_mes</t>
+          <t>custos[10].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="D435" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[10].duracao_meses</t>
+          <t>custos[10].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="D437" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].grupo</t>
+          <t>custos[11].grupo</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="D438" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].categoria</t>
+          <t>custos[11].categoria</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="D439" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].subcategoria</t>
+          <t>custos[11].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="D440" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_unidade</t>
+          <t>custos[11].unidade</t>
         </is>
       </c>
     </row>
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D441" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[11].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8432,7 +8432,7 @@
       </c>
       <c r="D442" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[11].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8449,12 +8449,12 @@
       </c>
       <c r="C443" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D443" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].curva_id / distribuicao_modo</t>
+          <t>custos[11].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="D444" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].cronograma_evento / fase_ancora_id</t>
+          <t>custos[11].cronograma</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="D445" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].inicio_mes</t>
+          <t>custos[11].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="D446" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[11].duracao_meses</t>
+          <t>custos[11].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D448" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].grupo</t>
+          <t>custos[12].grupo</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="D449" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].categoria</t>
+          <t>custos[12].categoria</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="D450" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].subcategoria</t>
+          <t>custos[12].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D451" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_unidade</t>
+          <t>custos[12].unidade</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="D452" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[12].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8629,7 +8629,7 @@
       </c>
       <c r="D453" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[12].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8642,12 +8642,12 @@
       <c r="B454" s="6" t="n"/>
       <c r="C454" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D454" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].curva_id / distribuicao_modo</t>
+          <t>custos[12].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="D455" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].cronograma_evento / fase_ancora_id</t>
+          <t>custos[12].cronograma</t>
         </is>
       </c>
     </row>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="D456" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].inicio_mes</t>
+          <t>custos[12].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D457" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[12].duracao_meses</t>
+          <t>custos[12].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="D459" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].grupo</t>
+          <t>custos[13].grupo</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="D460" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].categoria</t>
+          <t>custos[13].categoria</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="D461" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].subcategoria</t>
+          <t>custos[13].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="D462" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_unidade</t>
+          <t>custos[13].unidade</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8797,7 @@
       </c>
       <c r="D463" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[13].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="D464" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[13].valor_pct</t>
         </is>
       </c>
     </row>
@@ -8827,12 +8827,12 @@
       <c r="B465" s="6" t="n"/>
       <c r="C465" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D465" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].curva_id / distribuicao_modo</t>
+          <t>custos[13].distribuicao</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8850,7 @@
       </c>
       <c r="D466" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].cronograma_evento / fase_ancora_id</t>
+          <t>custos[13].cronograma</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="D467" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].inicio_mes</t>
+          <t>custos[13].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="D468" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[13].duracao_meses</t>
+          <t>custos[13].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="D470" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].grupo</t>
+          <t>custos[14].grupo</t>
         </is>
       </c>
     </row>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="D471" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].categoria</t>
+          <t>custos[14].categoria</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8947,7 @@
       </c>
       <c r="D472" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].subcategoria</t>
+          <t>custos[14].subcategoria</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="D473" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_unidade</t>
+          <t>custos[14].unidade</t>
         </is>
       </c>
     </row>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="D474" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[14].valor_rs</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="D475" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[14].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9012,12 +9012,12 @@
       <c r="B476" s="6" t="n"/>
       <c r="C476" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D476" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].curva_id / distribuicao_modo</t>
+          <t>custos[14].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="D477" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].cronograma_evento / fase_ancora_id</t>
+          <t>custos[14].cronograma</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D478" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].inicio_mes</t>
+          <t>custos[14].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="D479" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[14].duracao_meses</t>
+          <t>custos[14].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="D481" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].grupo</t>
+          <t>custos[15].grupo</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="D482" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].categoria</t>
+          <t>custos[15].categoria</t>
         </is>
       </c>
     </row>
@@ -9132,7 +9132,7 @@
       </c>
       <c r="D483" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].subcategoria</t>
+          <t>custos[15].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="D484" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_unidade</t>
+          <t>custos[15].unidade</t>
         </is>
       </c>
     </row>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="D485" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[15].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="D486" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[15].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9197,12 +9197,12 @@
       <c r="B487" s="6" t="n"/>
       <c r="C487" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D487" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].curva_id / distribuicao_modo</t>
+          <t>custos[15].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9220,7 +9220,7 @@
       </c>
       <c r="D488" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].cronograma_evento / fase_ancora_id</t>
+          <t>custos[15].cronograma</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="D489" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].inicio_mes</t>
+          <t>custos[15].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="D490" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[15].duracao_meses</t>
+          <t>custos[15].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D492" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].grupo</t>
+          <t>custos[16].grupo</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="D493" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].categoria</t>
+          <t>custos[16].categoria</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
       </c>
       <c r="D494" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].subcategoria</t>
+          <t>custos[16].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="D495" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_unidade</t>
+          <t>custos[16].unidade</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       </c>
       <c r="D496" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[16].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9369,7 +9369,7 @@
       </c>
       <c r="D497" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[16].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9382,12 +9382,12 @@
       <c r="B498" s="6" t="n"/>
       <c r="C498" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D498" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].curva_id / distribuicao_modo</t>
+          <t>custos[16].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="D499" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].cronograma_evento / fase_ancora_id</t>
+          <t>custos[16].cronograma</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="D500" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].inicio_mes</t>
+          <t>custos[16].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9441,7 @@
       </c>
       <c r="D501" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[16].duracao_meses</t>
+          <t>custos[16].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="D503" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].grupo</t>
+          <t>custos[17].grupo</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="D504" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].categoria</t>
+          <t>custos[17].categoria</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="D505" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].subcategoria</t>
+          <t>custos[17].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="D506" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_unidade</t>
+          <t>custos[17].unidade</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="D507" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[17].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="D508" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[17].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9567,12 +9567,12 @@
       <c r="B509" s="6" t="n"/>
       <c r="C509" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D509" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].curva_id / distribuicao_modo</t>
+          <t>custos[17].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="D510" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].cronograma_evento / fase_ancora_id</t>
+          <t>custos[17].cronograma</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
       </c>
       <c r="D511" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].inicio_mes</t>
+          <t>custos[17].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9626,7 +9626,7 @@
       </c>
       <c r="D512" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[17].duracao_meses</t>
+          <t>custos[17].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="D514" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].grupo</t>
+          <t>custos[18].grupo</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9669,7 @@
       </c>
       <c r="D515" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].categoria</t>
+          <t>custos[18].categoria</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9687,7 @@
       </c>
       <c r="D516" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].subcategoria</t>
+          <t>custos[18].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="D517" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_unidade</t>
+          <t>custos[18].unidade</t>
         </is>
       </c>
     </row>
@@ -9722,7 +9722,7 @@
       </c>
       <c r="D518" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[18].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="D519" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[18].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9752,12 +9752,12 @@
       <c r="B520" s="6" t="n"/>
       <c r="C520" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D520" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].curva_id / distribuicao_modo</t>
+          <t>custos[18].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="D521" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].cronograma_evento / fase_ancora_id</t>
+          <t>custos[18].cronograma</t>
         </is>
       </c>
     </row>
@@ -9793,7 +9793,7 @@
       </c>
       <c r="D522" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].inicio_mes</t>
+          <t>custos[18].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="D523" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[18].duracao_meses</t>
+          <t>custos[18].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="D525" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].grupo</t>
+          <t>custos[19].grupo</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="D526" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].categoria</t>
+          <t>custos[19].categoria</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="D527" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].subcategoria</t>
+          <t>custos[19].subcategoria</t>
         </is>
       </c>
     </row>
@@ -9890,7 +9890,7 @@
       </c>
       <c r="D528" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_unidade</t>
+          <t>custos[19].unidade</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="D529" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[19].valor_rs</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9924,7 @@
       </c>
       <c r="D530" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[19].valor_pct</t>
         </is>
       </c>
     </row>
@@ -9937,12 +9937,12 @@
       <c r="B531" s="6" t="n"/>
       <c r="C531" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D531" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].curva_id / distribuicao_modo</t>
+          <t>custos[19].distribuicao</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="D532" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].cronograma_evento / fase_ancora_id</t>
+          <t>custos[19].cronograma</t>
         </is>
       </c>
     </row>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D533" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].inicio_mes</t>
+          <t>custos[19].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="D534" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[19].duracao_meses</t>
+          <t>custos[19].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10021,7 +10021,7 @@
       </c>
       <c r="D536" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].grupo</t>
+          <t>custos[20].grupo</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="D537" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].categoria</t>
+          <t>custos[20].categoria</t>
         </is>
       </c>
     </row>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="D538" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].subcategoria</t>
+          <t>custos[20].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="D539" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_unidade</t>
+          <t>custos[20].unidade</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="D540" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[20].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D541" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[20].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       <c r="B542" s="6" t="n"/>
       <c r="C542" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D542" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].curva_id / distribuicao_modo</t>
+          <t>custos[20].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="D543" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].cronograma_evento / fase_ancora_id</t>
+          <t>custos[20].cronograma</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D544" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].inicio_mes</t>
+          <t>custos[20].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D545" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[20].duracao_meses</t>
+          <t>custos[20].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="D547" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].grupo</t>
+          <t>custos[21].grupo</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="D548" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].categoria</t>
+          <t>custos[21].categoria</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="D549" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].subcategoria</t>
+          <t>custos[21].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="D550" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_unidade</t>
+          <t>custos[21].unidade</t>
         </is>
       </c>
     </row>
@@ -10277,7 +10277,7 @@
       </c>
       <c r="D551" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[21].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10294,7 +10294,7 @@
       </c>
       <c r="D552" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[21].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10307,12 +10307,12 @@
       <c r="B553" s="6" t="n"/>
       <c r="C553" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D553" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].curva_id / distribuicao_modo</t>
+          <t>custos[21].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10330,7 @@
       </c>
       <c r="D554" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].cronograma_evento / fase_ancora_id</t>
+          <t>custos[21].cronograma</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D555" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].inicio_mes</t>
+          <t>custos[21].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D556" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[21].duracao_meses</t>
+          <t>custos[21].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="D558" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].grupo</t>
+          <t>custos[22].grupo</t>
         </is>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="D559" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].categoria</t>
+          <t>custos[22].categoria</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="D560" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].subcategoria</t>
+          <t>custos[22].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="D561" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_unidade</t>
+          <t>custos[22].unidade</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="D562" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[22].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10479,7 +10479,7 @@
       </c>
       <c r="D563" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[22].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10492,12 +10492,12 @@
       <c r="B564" s="6" t="n"/>
       <c r="C564" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D564" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].curva_id / distribuicao_modo</t>
+          <t>custos[22].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="D565" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].cronograma_evento / fase_ancora_id</t>
+          <t>custos[22].cronograma</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D566" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].inicio_mes</t>
+          <t>custos[22].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="D567" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[22].duracao_meses</t>
+          <t>custos[22].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="D569" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].grupo</t>
+          <t>custos[23].grupo</t>
         </is>
       </c>
     </row>
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D570" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].categoria</t>
+          <t>custos[23].categoria</t>
         </is>
       </c>
     </row>
@@ -10612,7 +10612,7 @@
       </c>
       <c r="D571" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].subcategoria</t>
+          <t>custos[23].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10630,7 @@
       </c>
       <c r="D572" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_unidade</t>
+          <t>custos[23].unidade</t>
         </is>
       </c>
     </row>
@@ -10647,7 +10647,7 @@
       </c>
       <c r="D573" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[23].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="D574" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[23].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10677,12 +10677,12 @@
       <c r="B575" s="6" t="n"/>
       <c r="C575" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D575" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].curva_id / distribuicao_modo</t>
+          <t>custos[23].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="D576" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].cronograma_evento / fase_ancora_id</t>
+          <t>custos[23].cronograma</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10718,7 @@
       </c>
       <c r="D577" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].inicio_mes</t>
+          <t>custos[23].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="D578" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[23].duracao_meses</t>
+          <t>custos[23].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10761,7 +10761,7 @@
       </c>
       <c r="D580" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].grupo</t>
+          <t>custos[24].grupo</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="D581" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].categoria</t>
+          <t>custos[24].categoria</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="D582" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].subcategoria</t>
+          <t>custos[24].subcategoria</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="D583" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_unidade</t>
+          <t>custos[24].unidade</t>
         </is>
       </c>
     </row>
@@ -10832,7 +10832,7 @@
       </c>
       <c r="D584" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[24].valor_rs</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
       </c>
       <c r="D585" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[24].valor_pct</t>
         </is>
       </c>
     </row>
@@ -10862,12 +10862,12 @@
       <c r="B586" s="6" t="n"/>
       <c r="C586" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D586" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].curva_id / distribuicao_modo</t>
+          <t>custos[24].distribuicao</t>
         </is>
       </c>
     </row>
@@ -10885,7 +10885,7 @@
       </c>
       <c r="D587" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].cronograma_evento / fase_ancora_id</t>
+          <t>custos[24].cronograma</t>
         </is>
       </c>
     </row>
@@ -10903,7 +10903,7 @@
       </c>
       <c r="D588" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].inicio_mes</t>
+          <t>custos[24].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -10921,7 +10921,7 @@
       </c>
       <c r="D589" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[24].duracao_meses</t>
+          <t>custos[24].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="D591" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].grupo</t>
+          <t>custos[25].grupo</t>
         </is>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
       </c>
       <c r="D592" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].categoria</t>
+          <t>custos[25].categoria</t>
         </is>
       </c>
     </row>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="D593" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].subcategoria</t>
+          <t>custos[25].subcategoria</t>
         </is>
       </c>
     </row>
@@ -11000,7 +11000,7 @@
       </c>
       <c r="D594" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_unidade</t>
+          <t>custos[25].unidade</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="D595" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[25].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11034,7 +11034,7 @@
       </c>
       <c r="D596" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[25].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11047,12 +11047,12 @@
       <c r="B597" s="6" t="n"/>
       <c r="C597" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D597" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].curva_id / distribuicao_modo</t>
+          <t>custos[25].distribuicao</t>
         </is>
       </c>
     </row>
@@ -11070,7 +11070,7 @@
       </c>
       <c r="D598" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].cronograma_evento / fase_ancora_id</t>
+          <t>custos[25].cronograma</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="D599" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].inicio_mes</t>
+          <t>custos[25].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D600" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[25].duracao_meses</t>
+          <t>custos[25].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -11131,7 +11131,7 @@
       </c>
       <c r="D602" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].grupo</t>
+          <t>custos[26].grupo</t>
         </is>
       </c>
     </row>
@@ -11149,7 +11149,7 @@
       </c>
       <c r="D603" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].categoria</t>
+          <t>custos[26].categoria</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="D604" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].subcategoria</t>
+          <t>custos[26].subcategoria</t>
         </is>
       </c>
     </row>
@@ -11185,7 +11185,7 @@
       </c>
       <c r="D605" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_unidade</t>
+          <t>custos[26].unidade</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="D606" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[26].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="D607" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[26].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11232,12 +11232,12 @@
       <c r="B608" s="6" t="n"/>
       <c r="C608" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D608" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].curva_id / distribuicao_modo</t>
+          <t>custos[26].distribuicao</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="D609" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].cronograma_evento / fase_ancora_id</t>
+          <t>custos[26].cronograma</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11273,7 @@
       </c>
       <c r="D610" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].inicio_mes</t>
+          <t>custos[26].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11291,7 @@
       </c>
       <c r="D611" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[26].duracao_meses</t>
+          <t>custos[26].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="D613" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].grupo</t>
+          <t>custos[27].grupo</t>
         </is>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="D614" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].categoria</t>
+          <t>custos[27].categoria</t>
         </is>
       </c>
     </row>
@@ -11352,7 +11352,7 @@
       </c>
       <c r="D615" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].subcategoria</t>
+          <t>custos[27].subcategoria</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11370,7 @@
       </c>
       <c r="D616" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_unidade</t>
+          <t>custos[27].unidade</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="D617" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[27].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="D618" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[27].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11417,12 +11417,12 @@
       <c r="B619" s="6" t="n"/>
       <c r="C619" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D619" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].curva_id / distribuicao_modo</t>
+          <t>custos[27].distribuicao</t>
         </is>
       </c>
     </row>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="D620" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].cronograma_evento / fase_ancora_id</t>
+          <t>custos[27].cronograma</t>
         </is>
       </c>
     </row>
@@ -11458,7 +11458,7 @@
       </c>
       <c r="D621" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].inicio_mes</t>
+          <t>custos[27].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="D622" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[27].duracao_meses</t>
+          <t>custos[27].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="D624" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].grupo</t>
+          <t>custos[28].grupo</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="D625" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].categoria</t>
+          <t>custos[28].categoria</t>
         </is>
       </c>
     </row>
@@ -11537,7 +11537,7 @@
       </c>
       <c r="D626" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].subcategoria</t>
+          <t>custos[28].subcategoria</t>
         </is>
       </c>
     </row>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="D627" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_unidade</t>
+          <t>custos[28].unidade</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11572,7 @@
       </c>
       <c r="D628" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_valor (se unidade = rs*)</t>
+          <t>custos[28].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="D629" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].orcamento_valor (se unidade = pct_*; em pontos)</t>
+          <t>custos[28].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11602,12 +11602,12 @@
       <c r="B630" s="6" t="n"/>
       <c r="C630" s="7" t="inlineStr">
         <is>
-          <t>Linear | nome da curva (ex.: Curva S) | unit_delivery | sales_revenue</t>
+          <t>Linear | nome de uma curva do catálogo (ex.: Curva S) | unit_delivery | sales_revenue</t>
         </is>
       </c>
       <c r="D630" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].curva_id / distribuicao_modo</t>
+          <t>custos[28].distribuicao</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11625,7 @@
       </c>
       <c r="D631" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].cronograma_evento / fase_ancora_id</t>
+          <t>custos[28].cronograma</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="D632" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].inicio_mes</t>
+          <t>custos[28].inicio_mes</t>
         </is>
       </c>
     </row>
@@ -11661,7 +11661,7 @@
       </c>
       <c r="D633" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[28].duracao_meses</t>
+          <t>custos[28].duracao_meses</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="D635" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#1].permuta_tipologia_id</t>
+          <t>permuta_fisica[1].tipologia</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11710,7 @@
       </c>
       <c r="D636" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#1].permuta_quantidade</t>
+          <t>permuta_fisica[1].unidades</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="D637" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#2].permuta_tipologia_id</t>
+          <t>permuta_fisica[2].tipologia</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="D638" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_fisica#2].permuta_quantidade</t>
+          <t>permuta_fisica[2].unidades</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="D640" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_unidade</t>
+          <t>permuta_financeira[1].unidade</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="D641" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_valor</t>
+          <t>permuta_financeira[1].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="D642" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].orcamento_valor</t>
+          <t>permuta_financeira[1].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="D643" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].permuta_financeira_deduzir_imposto</t>
+          <t>permuta_financeira[1].deduzir_imposto</t>
         </is>
       </c>
     </row>
@@ -11857,7 +11857,7 @@
       </c>
       <c r="D644" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#1].permuta_financeira_deduzir_corretagem</t>
+          <t>permuta_financeira[1].deduzir_corretagem</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="D645" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_unidade</t>
+          <t>permuta_financeira[2].unidade</t>
         </is>
       </c>
     </row>
@@ -11893,7 +11893,7 @@
       </c>
       <c r="D646" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_valor</t>
+          <t>permuta_financeira[2].valor_rs</t>
         </is>
       </c>
     </row>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="D647" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].orcamento_valor</t>
+          <t>permuta_financeira[2].valor_pct</t>
         </is>
       </c>
     </row>
@@ -11929,7 +11929,7 @@
       </c>
       <c r="D648" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].permuta_financeira_deduzir_imposto</t>
+          <t>permuta_financeira[2].deduzir_imposto</t>
         </is>
       </c>
     </row>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="D649" s="8" t="inlineStr">
         <is>
-          <t>avancado_linhas_custo[permuta_financeira#2].permuta_financeira_deduzir_corretagem</t>
+          <t>permuta_financeira[2].deduzir_corretagem</t>
         </is>
       </c>
     </row>
@@ -11983,7 +11983,7 @@
       </c>
       <c r="D652" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].nome</t>
+          <t>funding.financiamento_producao.nome</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="D653" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].ativo</t>
+          <t>funding.financiamento_producao.ativo</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="D654" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].valor</t>
+          <t>funding.financiamento_producao.valor</t>
         </is>
       </c>
     </row>
@@ -12045,7 +12045,7 @@
       </c>
       <c r="D655" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].taxa_anual</t>
+          <t>funding.financiamento_producao.taxa_anual</t>
         </is>
       </c>
     </row>
@@ -12065,7 +12065,7 @@
       </c>
       <c r="D656" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].exposicao_minima</t>
+          <t>funding.financiamento_producao.exposicao_minima</t>
         </is>
       </c>
     </row>
@@ -12085,7 +12085,7 @@
       </c>
       <c r="D657" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].percentual_financiavel</t>
+          <t>funding.financiamento_producao.percentual_financiavel</t>
         </is>
       </c>
     </row>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="D658" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].amortizar_com_caixa_disponivel</t>
+          <t>funding.financiamento_producao.amortizar_com_caixa_disponivel</t>
         </is>
       </c>
     </row>
@@ -12124,12 +12124,12 @@
       </c>
       <c r="C659" s="7" t="inlineStr">
         <is>
-          <t>linhas de custo (texto); vazio = padrão</t>
+          <t>linhas de custo separadas por ";" — Categoria ou Categoria / Subcategoria; vazio = padrão</t>
         </is>
       </c>
       <c r="D659" s="8" t="inlineStr">
         <is>
-          <t>funding[financiamento_producao].custo_linha_ids</t>
+          <t>funding.financiamento_producao.base_financiavel</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="D661" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].nome</t>
+          <t>funding.divida[1].nome</t>
         </is>
       </c>
     </row>
@@ -12178,7 +12178,7 @@
       </c>
       <c r="D662" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].valor</t>
+          <t>funding.divida[1].valor</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12200,7 @@
       </c>
       <c r="D663" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[1].aporte</t>
         </is>
       </c>
     </row>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="D664" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].inicio_mes</t>
+          <t>funding.divida[1].mes</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12242,7 @@
       </c>
       <c r="D665" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].distribuir_aporte</t>
+          <t>funding.divida[1].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12262,7 @@
       </c>
       <c r="D666" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].aporte_meses</t>
+          <t>funding.divida[1].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12282,7 @@
       </c>
       <c r="D667" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_anual</t>
+          <t>funding.divida[1].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12302,7 @@
       </c>
       <c r="D668" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].periodo_amortizacao_meses</t>
+          <t>funding.divida[1].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="D669" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].periodo_carencia_meses</t>
+          <t>funding.divida[1].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -12342,7 +12342,7 @@
       </c>
       <c r="D670" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_estruturacao_pct</t>
+          <t>funding.divida[1].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="D671" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].taxa_administracao_mensal</t>
+          <t>funding.divida[1].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="D672" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#1].outros_encargos_iniciais</t>
+          <t>funding.divida[1].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -12407,7 +12407,7 @@
       </c>
       <c r="D674" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].nome</t>
+          <t>funding.divida[2].nome</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="D675" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].valor</t>
+          <t>funding.divida[2].valor</t>
         </is>
       </c>
     </row>
@@ -12443,7 +12443,7 @@
       </c>
       <c r="D676" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[2].aporte</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="D677" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].inicio_mes</t>
+          <t>funding.divida[2].mes</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="D678" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].distribuir_aporte</t>
+          <t>funding.divida[2].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -12497,7 +12497,7 @@
       </c>
       <c r="D679" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].aporte_meses</t>
+          <t>funding.divida[2].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12515,7 @@
       </c>
       <c r="D680" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_anual</t>
+          <t>funding.divida[2].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="D681" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].periodo_amortizacao_meses</t>
+          <t>funding.divida[2].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D682" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].periodo_carencia_meses</t>
+          <t>funding.divida[2].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="D683" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_estruturacao_pct</t>
+          <t>funding.divida[2].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="D684" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].taxa_administracao_mensal</t>
+          <t>funding.divida[2].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="D685" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#2].outros_encargos_iniciais</t>
+          <t>funding.divida[2].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="D687" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].nome</t>
+          <t>funding.divida[3].nome</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="D688" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].valor</t>
+          <t>funding.divida[3].valor</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="D689" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].cronograma_evento / fase_ancora_id</t>
+          <t>funding.divida[3].aporte</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="D690" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].inicio_mes</t>
+          <t>funding.divida[3].mes</t>
         </is>
       </c>
     </row>
@@ -12702,7 +12702,7 @@
       </c>
       <c r="D691" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].distribuir_aporte</t>
+          <t>funding.divida[3].distribuir_aporte</t>
         </is>
       </c>
     </row>
@@ -12720,7 +12720,7 @@
       </c>
       <c r="D692" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].aporte_meses</t>
+          <t>funding.divida[3].aporte_meses</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="D693" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_anual</t>
+          <t>funding.divida[3].taxa_anual</t>
         </is>
       </c>
     </row>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="D694" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].periodo_amortizacao_meses</t>
+          <t>funding.divida[3].amortizacao_meses</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="D695" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].periodo_carencia_meses</t>
+          <t>funding.divida[3].carencia_meses</t>
         </is>
       </c>
     </row>
@@ -12792,7 +12792,7 @@
       </c>
       <c r="D696" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_estruturacao_pct</t>
+          <t>funding.divida[3].estruturacao_pct</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="D697" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].taxa_administracao_mensal</t>
+          <t>funding.divida[3].administracao_mensal</t>
         </is>
       </c>
     </row>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="D698" s="8" t="inlineStr">
         <is>
-          <t>funding[divida#3].outros_encargos_iniciais</t>
+          <t>funding.divida[3].outros_encargos</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="D700" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].nome</t>
+          <t>funding.equity[1].nome</t>
         </is>
       </c>
     </row>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="D701" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].valor</t>
+          <t>funding.equity[1].valor</t>
         </is>
       </c>
     </row>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="D702" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[1].aporte</t>
         </is>
       </c>
     </row>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="D703" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].inicio_mes</t>
+          <t>funding.equity[1].mes</t>
         </is>
       </c>
     </row>
@@ -12939,7 +12939,7 @@
       </c>
       <c r="D704" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].modo_retorno</t>
+          <t>funding.equity[1].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="D705" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#1].pct_retorno</t>
+          <t>funding.equity[1].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12984,7 @@
       </c>
       <c r="D707" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].nome</t>
+          <t>funding.equity[2].nome</t>
         </is>
       </c>
     </row>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="D708" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].valor</t>
+          <t>funding.equity[2].valor</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="D709" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[2].aporte</t>
         </is>
       </c>
     </row>
@@ -13038,7 +13038,7 @@
       </c>
       <c r="D710" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].inicio_mes</t>
+          <t>funding.equity[2].mes</t>
         </is>
       </c>
     </row>
@@ -13056,7 +13056,7 @@
       </c>
       <c r="D711" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].modo_retorno</t>
+          <t>funding.equity[2].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="D712" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#2].pct_retorno</t>
+          <t>funding.equity[2].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="D714" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].nome</t>
+          <t>funding.equity[3].nome</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="D715" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].valor</t>
+          <t>funding.equity[3].valor</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13135,7 @@
       </c>
       <c r="D716" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].cronograma_evento / fase_ancora_id</t>
+          <t>funding.equity[3].aporte</t>
         </is>
       </c>
     </row>
@@ -13153,7 +13153,7 @@
       </c>
       <c r="D717" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].inicio_mes</t>
+          <t>funding.equity[3].mes</t>
         </is>
       </c>
     </row>
@@ -13171,7 +13171,7 @@
       </c>
       <c r="D718" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].modo_retorno</t>
+          <t>funding.equity[3].modo_retorno</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="D719" s="8" t="inlineStr">
         <is>
-          <t>funding[equity#3].pct_retorno</t>
+          <t>funding.equity[3].pct_retorno</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="D721" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].nome</t>
+          <t>cenarios[1].nome</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="D722" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].preco_venda_pct</t>
+          <t>cenarios[1].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="D723" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[1].custo_obra_pct</t>
+          <t>cenarios[1].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -13280,7 +13280,7 @@
       </c>
       <c r="D724" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].nome</t>
+          <t>cenarios[2].nome</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="D725" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].preco_venda_pct</t>
+          <t>cenarios[2].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="D726" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[2].custo_obra_pct</t>
+          <t>cenarios[2].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13338,7 @@
       </c>
       <c r="D727" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].nome</t>
+          <t>cenarios[3].nome</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="D728" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].preco_venda_pct</t>
+          <t>cenarios[3].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13374,7 @@
       </c>
       <c r="D729" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[3].custo_obra_pct</t>
+          <t>cenarios[3].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="D730" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].nome</t>
+          <t>cenarios[4].nome</t>
         </is>
       </c>
     </row>
@@ -13410,7 +13410,7 @@
       </c>
       <c r="D731" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].preco_venda_pct</t>
+          <t>cenarios[4].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="D732" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[4].custo_obra_pct</t>
+          <t>cenarios[4].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13446,7 @@
       </c>
       <c r="D733" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].nome</t>
+          <t>cenarios[5].nome</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="D734" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].preco_venda_pct</t>
+          <t>cenarios[5].preco_venda_pct</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="D735" s="8" t="inlineStr">
         <is>
-          <t>avancado_cenarios[5].custo_obra_pct</t>
+          <t>cenarios[5].custo_obra_pct</t>
         </is>
       </c>
     </row>
@@ -16310,16 +16310,16 @@
     <row r="875">
       <c r="A875" s="19" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — terreno</t>
-        </is>
-      </c>
-      <c r="B875" s="25">
-        <f>IF($B$327="terreno",N($B$847),0)+IF($B$338="terreno",N($B$848),0)+IF($B$349="terreno",N($B$849),0)+IF($B$360="terreno",N($B$850),0)+IF($B$371="terreno",N($B$851),0)+IF($B$382="terreno",N($B$852),0)+IF($B$393="terreno",N($B$853),0)+IF($B$404="terreno",N($B$854),0)+IF($B$415="terreno",N($B$855),0)+IF($B$426="terreno",N($B$856),0)+IF($B$437="terreno",N($B$857),0)+IF($B$448="terreno",N($B$858),0)+IF($B$459="terreno",N($B$859),0)+IF($B$470="terreno",N($B$860),0)+IF($B$481="terreno",N($B$861),0)+IF($B$492="terreno",N($B$862),0)+IF($B$503="terreno",N($B$863),0)+IF($B$514="terreno",N($B$864),0)+IF($B$525="terreno",N($B$865),0)+IF($B$536="terreno",N($B$866),0)+IF($B$547="terreno",N($B$867),0)+IF($B$558="terreno",N($B$868),0)+IF($B$569="terreno",N($B$869),0)+IF($B$580="terreno",N($B$870),0)+IF($B$591="terreno",N($B$871),0)+IF($B$602="terreno",N($B$872),0)+IF($B$613="terreno",N($B$873),0)+IF($B$624="terreno",N($B$874),0)</f>
+          <t>Custo 1 — conferência</t>
+        </is>
+      </c>
+      <c r="B875" s="24">
+        <f>IF(AND($B$327="",$B$328=""),"",IF(OR($B$327="",$B$328="",$B$330=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$327="terreno",$B$328="Preço",OR($B$330="rs",$B$330="rs_m2_terreno")),AND($B$327="terreno",$B$328="Registro",OR($B$330="rs",$B$330="rs_m2_priv")),AND($B$327="terreno",$B$328="Outro",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="obra",$B$328="Construção",OR($B$330="rs",$B$330="rs_m2_priv")),AND($B$327="obra",$B$328="Outorga",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="obra",$B$328="Decoração",OR($B$330="rs",$B$330="rs_m2_priv")),AND($B$327="obra",$B$328="Gestão da obra",OR($B$330="rs",$B$330="pct_obra")),AND($B$327="obra",$B$328="Contingência",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="obra",$B$328="Outro",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="diretos",$B$328="Marketing &amp; Publicidade",OR($B$330="rs",$B$330="pct_vgv",$B$330="pct_recebido")),AND($B$327="diretos",$B$328="Corretagem de vendas",OR($B$330="pct_vgv")),AND($B$327="diretos",$B$328="Projetos",OR($B$330="rs",$B$330="rs_m2_priv",$B$330="pct_constr")),AND($B$327="diretos",$B$328="Licenças e Aprovações",OR($B$330="rs",$B$330="rs_m2_priv")),AND($B$327="diretos",$B$328="Manutenção pós-obra",OR($B$330="rs",$B$330="pct_vgv",$B$330="pct_recebido")),AND($B$327="diretos",$B$328="Outro",OR($B$330="rs",$B$330="pct_vgv",$B$330="pct_recebido")),AND($B$327="indireto",$B$328="Marketing global",OR($B$330="rs",$B$330="pct_vgv",$B$330="pct_recebido")),AND($B$327="indireto",$B$328="Stand de vendas",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="indireto",$B$328="Gestão",OR($B$330="rs",$B$330="pct_vgv",$B$330="pct_recebido")),AND($B$327="indireto",$B$328="Outro",OR($B$330="rs",$B$330="pct_vgv",$B$330="pct_recebido")),AND($B$327="financeiro",$B$328="Juros de financiamento",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="financeiro",$B$328="Taxas bancárias",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="financeiro",$B$328="Estruturação de dívida",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="financeiro",$B$328="Investidores",OR($B$330="rs",$B$330="pct_vgv")),AND($B$327="financeiro",$B$328="Outro",OR($B$330="rs",$B$330="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$331&lt;&gt;"",$B$332&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$330,3)="pct",$B$332="",$B$331=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C875" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D875" s="22" t="inlineStr">
@@ -16331,16 +16331,16 @@
     <row r="876">
       <c r="A876" s="19" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — obra</t>
-        </is>
-      </c>
-      <c r="B876" s="25">
-        <f>IF($B$327="obra",N($B$847),0)+IF($B$338="obra",N($B$848),0)+IF($B$349="obra",N($B$849),0)+IF($B$360="obra",N($B$850),0)+IF($B$371="obra",N($B$851),0)+IF($B$382="obra",N($B$852),0)+IF($B$393="obra",N($B$853),0)+IF($B$404="obra",N($B$854),0)+IF($B$415="obra",N($B$855),0)+IF($B$426="obra",N($B$856),0)+IF($B$437="obra",N($B$857),0)+IF($B$448="obra",N($B$858),0)+IF($B$459="obra",N($B$859),0)+IF($B$470="obra",N($B$860),0)+IF($B$481="obra",N($B$861),0)+IF($B$492="obra",N($B$862),0)+IF($B$503="obra",N($B$863),0)+IF($B$514="obra",N($B$864),0)+IF($B$525="obra",N($B$865),0)+IF($B$536="obra",N($B$866),0)+IF($B$547="obra",N($B$867),0)+IF($B$558="obra",N($B$868),0)+IF($B$569="obra",N($B$869),0)+IF($B$580="obra",N($B$870),0)+IF($B$591="obra",N($B$871),0)+IF($B$602="obra",N($B$872),0)+IF($B$613="obra",N($B$873),0)+IF($B$624="obra",N($B$874),0)</f>
+          <t>Custo 2 — conferência</t>
+        </is>
+      </c>
+      <c r="B876" s="24">
+        <f>IF(AND($B$338="",$B$339=""),"",IF(OR($B$338="",$B$339="",$B$341=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$338="terreno",$B$339="Preço",OR($B$341="rs",$B$341="rs_m2_terreno")),AND($B$338="terreno",$B$339="Registro",OR($B$341="rs",$B$341="rs_m2_priv")),AND($B$338="terreno",$B$339="Outro",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="obra",$B$339="Construção",OR($B$341="rs",$B$341="rs_m2_priv")),AND($B$338="obra",$B$339="Outorga",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="obra",$B$339="Decoração",OR($B$341="rs",$B$341="rs_m2_priv")),AND($B$338="obra",$B$339="Gestão da obra",OR($B$341="rs",$B$341="pct_obra")),AND($B$338="obra",$B$339="Contingência",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="obra",$B$339="Outro",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="diretos",$B$339="Marketing &amp; Publicidade",OR($B$341="rs",$B$341="pct_vgv",$B$341="pct_recebido")),AND($B$338="diretos",$B$339="Corretagem de vendas",OR($B$341="pct_vgv")),AND($B$338="diretos",$B$339="Projetos",OR($B$341="rs",$B$341="rs_m2_priv",$B$341="pct_constr")),AND($B$338="diretos",$B$339="Licenças e Aprovações",OR($B$341="rs",$B$341="rs_m2_priv")),AND($B$338="diretos",$B$339="Manutenção pós-obra",OR($B$341="rs",$B$341="pct_vgv",$B$341="pct_recebido")),AND($B$338="diretos",$B$339="Outro",OR($B$341="rs",$B$341="pct_vgv",$B$341="pct_recebido")),AND($B$338="indireto",$B$339="Marketing global",OR($B$341="rs",$B$341="pct_vgv",$B$341="pct_recebido")),AND($B$338="indireto",$B$339="Stand de vendas",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="indireto",$B$339="Gestão",OR($B$341="rs",$B$341="pct_vgv",$B$341="pct_recebido")),AND($B$338="indireto",$B$339="Outro",OR($B$341="rs",$B$341="pct_vgv",$B$341="pct_recebido")),AND($B$338="financeiro",$B$339="Juros de financiamento",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="financeiro",$B$339="Taxas bancárias",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="financeiro",$B$339="Estruturação de dívida",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="financeiro",$B$339="Investidores",OR($B$341="rs",$B$341="pct_vgv")),AND($B$338="financeiro",$B$339="Outro",OR($B$341="rs",$B$341="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$342&lt;&gt;"",$B$343&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$341,3)="pct",$B$343="",$B$342=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C876" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D876" s="22" t="inlineStr">
@@ -16352,16 +16352,16 @@
     <row r="877">
       <c r="A877" s="19" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — diretos</t>
-        </is>
-      </c>
-      <c r="B877" s="25">
-        <f>IF($B$327="diretos",N($B$847),0)+IF($B$338="diretos",N($B$848),0)+IF($B$349="diretos",N($B$849),0)+IF($B$360="diretos",N($B$850),0)+IF($B$371="diretos",N($B$851),0)+IF($B$382="diretos",N($B$852),0)+IF($B$393="diretos",N($B$853),0)+IF($B$404="diretos",N($B$854),0)+IF($B$415="diretos",N($B$855),0)+IF($B$426="diretos",N($B$856),0)+IF($B$437="diretos",N($B$857),0)+IF($B$448="diretos",N($B$858),0)+IF($B$459="diretos",N($B$859),0)+IF($B$470="diretos",N($B$860),0)+IF($B$481="diretos",N($B$861),0)+IF($B$492="diretos",N($B$862),0)+IF($B$503="diretos",N($B$863),0)+IF($B$514="diretos",N($B$864),0)+IF($B$525="diretos",N($B$865),0)+IF($B$536="diretos",N($B$866),0)+IF($B$547="diretos",N($B$867),0)+IF($B$558="diretos",N($B$868),0)+IF($B$569="diretos",N($B$869),0)+IF($B$580="diretos",N($B$870),0)+IF($B$591="diretos",N($B$871),0)+IF($B$602="diretos",N($B$872),0)+IF($B$613="diretos",N($B$873),0)+IF($B$624="diretos",N($B$874),0)</f>
+          <t>Custo 3 — conferência</t>
+        </is>
+      </c>
+      <c r="B877" s="24">
+        <f>IF(AND($B$349="",$B$350=""),"",IF(OR($B$349="",$B$350="",$B$352=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$349="terreno",$B$350="Preço",OR($B$352="rs",$B$352="rs_m2_terreno")),AND($B$349="terreno",$B$350="Registro",OR($B$352="rs",$B$352="rs_m2_priv")),AND($B$349="terreno",$B$350="Outro",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="obra",$B$350="Construção",OR($B$352="rs",$B$352="rs_m2_priv")),AND($B$349="obra",$B$350="Outorga",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="obra",$B$350="Decoração",OR($B$352="rs",$B$352="rs_m2_priv")),AND($B$349="obra",$B$350="Gestão da obra",OR($B$352="rs",$B$352="pct_obra")),AND($B$349="obra",$B$350="Contingência",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="obra",$B$350="Outro",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="diretos",$B$350="Marketing &amp; Publicidade",OR($B$352="rs",$B$352="pct_vgv",$B$352="pct_recebido")),AND($B$349="diretos",$B$350="Corretagem de vendas",OR($B$352="pct_vgv")),AND($B$349="diretos",$B$350="Projetos",OR($B$352="rs",$B$352="rs_m2_priv",$B$352="pct_constr")),AND($B$349="diretos",$B$350="Licenças e Aprovações",OR($B$352="rs",$B$352="rs_m2_priv")),AND($B$349="diretos",$B$350="Manutenção pós-obra",OR($B$352="rs",$B$352="pct_vgv",$B$352="pct_recebido")),AND($B$349="diretos",$B$350="Outro",OR($B$352="rs",$B$352="pct_vgv",$B$352="pct_recebido")),AND($B$349="indireto",$B$350="Marketing global",OR($B$352="rs",$B$352="pct_vgv",$B$352="pct_recebido")),AND($B$349="indireto",$B$350="Stand de vendas",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="indireto",$B$350="Gestão",OR($B$352="rs",$B$352="pct_vgv",$B$352="pct_recebido")),AND($B$349="indireto",$B$350="Outro",OR($B$352="rs",$B$352="pct_vgv",$B$352="pct_recebido")),AND($B$349="financeiro",$B$350="Juros de financiamento",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="financeiro",$B$350="Taxas bancárias",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="financeiro",$B$350="Estruturação de dívida",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="financeiro",$B$350="Investidores",OR($B$352="rs",$B$352="pct_vgv")),AND($B$349="financeiro",$B$350="Outro",OR($B$352="rs",$B$352="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$353&lt;&gt;"",$B$354&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$352,3)="pct",$B$354="",$B$353=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C877" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D877" s="22" t="inlineStr">
@@ -16373,16 +16373,16 @@
     <row r="878">
       <c r="A878" s="19" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — indireto</t>
-        </is>
-      </c>
-      <c r="B878" s="25">
-        <f>IF($B$327="indireto",N($B$847),0)+IF($B$338="indireto",N($B$848),0)+IF($B$349="indireto",N($B$849),0)+IF($B$360="indireto",N($B$850),0)+IF($B$371="indireto",N($B$851),0)+IF($B$382="indireto",N($B$852),0)+IF($B$393="indireto",N($B$853),0)+IF($B$404="indireto",N($B$854),0)+IF($B$415="indireto",N($B$855),0)+IF($B$426="indireto",N($B$856),0)+IF($B$437="indireto",N($B$857),0)+IF($B$448="indireto",N($B$858),0)+IF($B$459="indireto",N($B$859),0)+IF($B$470="indireto",N($B$860),0)+IF($B$481="indireto",N($B$861),0)+IF($B$492="indireto",N($B$862),0)+IF($B$503="indireto",N($B$863),0)+IF($B$514="indireto",N($B$864),0)+IF($B$525="indireto",N($B$865),0)+IF($B$536="indireto",N($B$866),0)+IF($B$547="indireto",N($B$867),0)+IF($B$558="indireto",N($B$868),0)+IF($B$569="indireto",N($B$869),0)+IF($B$580="indireto",N($B$870),0)+IF($B$591="indireto",N($B$871),0)+IF($B$602="indireto",N($B$872),0)+IF($B$613="indireto",N($B$873),0)+IF($B$624="indireto",N($B$874),0)</f>
+          <t>Custo 4 — conferência</t>
+        </is>
+      </c>
+      <c r="B878" s="24">
+        <f>IF(AND($B$360="",$B$361=""),"",IF(OR($B$360="",$B$361="",$B$363=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$360="terreno",$B$361="Preço",OR($B$363="rs",$B$363="rs_m2_terreno")),AND($B$360="terreno",$B$361="Registro",OR($B$363="rs",$B$363="rs_m2_priv")),AND($B$360="terreno",$B$361="Outro",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="obra",$B$361="Construção",OR($B$363="rs",$B$363="rs_m2_priv")),AND($B$360="obra",$B$361="Outorga",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="obra",$B$361="Decoração",OR($B$363="rs",$B$363="rs_m2_priv")),AND($B$360="obra",$B$361="Gestão da obra",OR($B$363="rs",$B$363="pct_obra")),AND($B$360="obra",$B$361="Contingência",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="obra",$B$361="Outro",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="diretos",$B$361="Marketing &amp; Publicidade",OR($B$363="rs",$B$363="pct_vgv",$B$363="pct_recebido")),AND($B$360="diretos",$B$361="Corretagem de vendas",OR($B$363="pct_vgv")),AND($B$360="diretos",$B$361="Projetos",OR($B$363="rs",$B$363="rs_m2_priv",$B$363="pct_constr")),AND($B$360="diretos",$B$361="Licenças e Aprovações",OR($B$363="rs",$B$363="rs_m2_priv")),AND($B$360="diretos",$B$361="Manutenção pós-obra",OR($B$363="rs",$B$363="pct_vgv",$B$363="pct_recebido")),AND($B$360="diretos",$B$361="Outro",OR($B$363="rs",$B$363="pct_vgv",$B$363="pct_recebido")),AND($B$360="indireto",$B$361="Marketing global",OR($B$363="rs",$B$363="pct_vgv",$B$363="pct_recebido")),AND($B$360="indireto",$B$361="Stand de vendas",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="indireto",$B$361="Gestão",OR($B$363="rs",$B$363="pct_vgv",$B$363="pct_recebido")),AND($B$360="indireto",$B$361="Outro",OR($B$363="rs",$B$363="pct_vgv",$B$363="pct_recebido")),AND($B$360="financeiro",$B$361="Juros de financiamento",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="financeiro",$B$361="Taxas bancárias",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="financeiro",$B$361="Estruturação de dívida",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="financeiro",$B$361="Investidores",OR($B$363="rs",$B$363="pct_vgv")),AND($B$360="financeiro",$B$361="Outro",OR($B$363="rs",$B$363="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$364&lt;&gt;"",$B$365&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$363,3)="pct",$B$365="",$B$364=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C878" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D878" s="22" t="inlineStr">
@@ -16394,16 +16394,16 @@
     <row r="879">
       <c r="A879" s="19" t="inlineStr">
         <is>
-          <t>Σ custos conversíveis — financeiro</t>
-        </is>
-      </c>
-      <c r="B879" s="25">
-        <f>IF($B$327="financeiro",N($B$847),0)+IF($B$338="financeiro",N($B$848),0)+IF($B$349="financeiro",N($B$849),0)+IF($B$360="financeiro",N($B$850),0)+IF($B$371="financeiro",N($B$851),0)+IF($B$382="financeiro",N($B$852),0)+IF($B$393="financeiro",N($B$853),0)+IF($B$404="financeiro",N($B$854),0)+IF($B$415="financeiro",N($B$855),0)+IF($B$426="financeiro",N($B$856),0)+IF($B$437="financeiro",N($B$857),0)+IF($B$448="financeiro",N($B$858),0)+IF($B$459="financeiro",N($B$859),0)+IF($B$470="financeiro",N($B$860),0)+IF($B$481="financeiro",N($B$861),0)+IF($B$492="financeiro",N($B$862),0)+IF($B$503="financeiro",N($B$863),0)+IF($B$514="financeiro",N($B$864),0)+IF($B$525="financeiro",N($B$865),0)+IF($B$536="financeiro",N($B$866),0)+IF($B$547="financeiro",N($B$867),0)+IF($B$558="financeiro",N($B$868),0)+IF($B$569="financeiro",N($B$869),0)+IF($B$580="financeiro",N($B$870),0)+IF($B$591="financeiro",N($B$871),0)+IF($B$602="financeiro",N($B$872),0)+IF($B$613="financeiro",N($B$873),0)+IF($B$624="financeiro",N($B$874),0)</f>
+          <t>Custo 5 — conferência</t>
+        </is>
+      </c>
+      <c r="B879" s="24">
+        <f>IF(AND($B$371="",$B$372=""),"",IF(OR($B$371="",$B$372="",$B$374=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$371="terreno",$B$372="Preço",OR($B$374="rs",$B$374="rs_m2_terreno")),AND($B$371="terreno",$B$372="Registro",OR($B$374="rs",$B$374="rs_m2_priv")),AND($B$371="terreno",$B$372="Outro",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="obra",$B$372="Construção",OR($B$374="rs",$B$374="rs_m2_priv")),AND($B$371="obra",$B$372="Outorga",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="obra",$B$372="Decoração",OR($B$374="rs",$B$374="rs_m2_priv")),AND($B$371="obra",$B$372="Gestão da obra",OR($B$374="rs",$B$374="pct_obra")),AND($B$371="obra",$B$372="Contingência",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="obra",$B$372="Outro",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="diretos",$B$372="Marketing &amp; Publicidade",OR($B$374="rs",$B$374="pct_vgv",$B$374="pct_recebido")),AND($B$371="diretos",$B$372="Corretagem de vendas",OR($B$374="pct_vgv")),AND($B$371="diretos",$B$372="Projetos",OR($B$374="rs",$B$374="rs_m2_priv",$B$374="pct_constr")),AND($B$371="diretos",$B$372="Licenças e Aprovações",OR($B$374="rs",$B$374="rs_m2_priv")),AND($B$371="diretos",$B$372="Manutenção pós-obra",OR($B$374="rs",$B$374="pct_vgv",$B$374="pct_recebido")),AND($B$371="diretos",$B$372="Outro",OR($B$374="rs",$B$374="pct_vgv",$B$374="pct_recebido")),AND($B$371="indireto",$B$372="Marketing global",OR($B$374="rs",$B$374="pct_vgv",$B$374="pct_recebido")),AND($B$371="indireto",$B$372="Stand de vendas",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="indireto",$B$372="Gestão",OR($B$374="rs",$B$374="pct_vgv",$B$374="pct_recebido")),AND($B$371="indireto",$B$372="Outro",OR($B$374="rs",$B$374="pct_vgv",$B$374="pct_recebido")),AND($B$371="financeiro",$B$372="Juros de financiamento",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="financeiro",$B$372="Taxas bancárias",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="financeiro",$B$372="Estruturação de dívida",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="financeiro",$B$372="Investidores",OR($B$374="rs",$B$374="pct_vgv")),AND($B$371="financeiro",$B$372="Outro",OR($B$374="rs",$B$374="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$375&lt;&gt;"",$B$376&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$374,3)="pct",$B$376="",$B$375=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C879" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D879" s="22" t="inlineStr">
@@ -16415,16 +16415,16 @@
     <row r="880">
       <c r="A880" s="19" t="inlineStr">
         <is>
-          <t>Permuta física 1 — VGV entregue (unidades × área × preço sugerido)</t>
-        </is>
-      </c>
-      <c r="B880" s="25">
-        <f>IF($B$635="",0,N($B$636)*(($B$59=$B$635)*(N($B$61)+N($B$62))*N($B$66)+($B$68=$B$635)*(N($B$70)+N($B$71))*N($B$75)+($B$77=$B$635)*(N($B$79)+N($B$80))*N($B$84)+($B$86=$B$635)*(N($B$88)+N($B$89))*N($B$93)+($B$95=$B$635)*(N($B$97)+N($B$98))*N($B$102)+($B$104=$B$635)*(N($B$106)+N($B$107))*N($B$111)+($B$113=$B$635)*(N($B$115)+N($B$116))*N($B$120)+($B$122=$B$635)*(N($B$124)+N($B$125))*N($B$129)+($B$131=$B$635)*(N($B$133)+N($B$134))*N($B$138)+($B$140=$B$635)*(N($B$142)+N($B$143))*N($B$147)))</f>
+          <t>Custo 6 — conferência</t>
+        </is>
+      </c>
+      <c r="B880" s="24">
+        <f>IF(AND($B$382="",$B$383=""),"",IF(OR($B$382="",$B$383="",$B$385=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$382="terreno",$B$383="Preço",OR($B$385="rs",$B$385="rs_m2_terreno")),AND($B$382="terreno",$B$383="Registro",OR($B$385="rs",$B$385="rs_m2_priv")),AND($B$382="terreno",$B$383="Outro",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="obra",$B$383="Construção",OR($B$385="rs",$B$385="rs_m2_priv")),AND($B$382="obra",$B$383="Outorga",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="obra",$B$383="Decoração",OR($B$385="rs",$B$385="rs_m2_priv")),AND($B$382="obra",$B$383="Gestão da obra",OR($B$385="rs",$B$385="pct_obra")),AND($B$382="obra",$B$383="Contingência",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="obra",$B$383="Outro",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="diretos",$B$383="Marketing &amp; Publicidade",OR($B$385="rs",$B$385="pct_vgv",$B$385="pct_recebido")),AND($B$382="diretos",$B$383="Corretagem de vendas",OR($B$385="pct_vgv")),AND($B$382="diretos",$B$383="Projetos",OR($B$385="rs",$B$385="rs_m2_priv",$B$385="pct_constr")),AND($B$382="diretos",$B$383="Licenças e Aprovações",OR($B$385="rs",$B$385="rs_m2_priv")),AND($B$382="diretos",$B$383="Manutenção pós-obra",OR($B$385="rs",$B$385="pct_vgv",$B$385="pct_recebido")),AND($B$382="diretos",$B$383="Outro",OR($B$385="rs",$B$385="pct_vgv",$B$385="pct_recebido")),AND($B$382="indireto",$B$383="Marketing global",OR($B$385="rs",$B$385="pct_vgv",$B$385="pct_recebido")),AND($B$382="indireto",$B$383="Stand de vendas",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="indireto",$B$383="Gestão",OR($B$385="rs",$B$385="pct_vgv",$B$385="pct_recebido")),AND($B$382="indireto",$B$383="Outro",OR($B$385="rs",$B$385="pct_vgv",$B$385="pct_recebido")),AND($B$382="financeiro",$B$383="Juros de financiamento",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="financeiro",$B$383="Taxas bancárias",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="financeiro",$B$383="Estruturação de dívida",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="financeiro",$B$383="Investidores",OR($B$385="rs",$B$385="pct_vgv")),AND($B$382="financeiro",$B$383="Outro",OR($B$385="rs",$B$385="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$386&lt;&gt;"",$B$387&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$385,3)="pct",$B$387="",$B$386=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C880" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D880" s="22" t="inlineStr">
@@ -16436,16 +16436,16 @@
     <row r="881">
       <c r="A881" s="19" t="inlineStr">
         <is>
-          <t>Permuta financeira 1 — equivalente em R$</t>
-        </is>
-      </c>
-      <c r="B881" s="25">
-        <f>IF($B$640="pct_vgv",N($B$642)*$B$788,IF($B$640="rs",N($B$641),0))</f>
+          <t>Custo 7 — conferência</t>
+        </is>
+      </c>
+      <c r="B881" s="24">
+        <f>IF(AND($B$393="",$B$394=""),"",IF(OR($B$393="",$B$394="",$B$396=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$393="terreno",$B$394="Preço",OR($B$396="rs",$B$396="rs_m2_terreno")),AND($B$393="terreno",$B$394="Registro",OR($B$396="rs",$B$396="rs_m2_priv")),AND($B$393="terreno",$B$394="Outro",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="obra",$B$394="Construção",OR($B$396="rs",$B$396="rs_m2_priv")),AND($B$393="obra",$B$394="Outorga",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="obra",$B$394="Decoração",OR($B$396="rs",$B$396="rs_m2_priv")),AND($B$393="obra",$B$394="Gestão da obra",OR($B$396="rs",$B$396="pct_obra")),AND($B$393="obra",$B$394="Contingência",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="obra",$B$394="Outro",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="diretos",$B$394="Marketing &amp; Publicidade",OR($B$396="rs",$B$396="pct_vgv",$B$396="pct_recebido")),AND($B$393="diretos",$B$394="Corretagem de vendas",OR($B$396="pct_vgv")),AND($B$393="diretos",$B$394="Projetos",OR($B$396="rs",$B$396="rs_m2_priv",$B$396="pct_constr")),AND($B$393="diretos",$B$394="Licenças e Aprovações",OR($B$396="rs",$B$396="rs_m2_priv")),AND($B$393="diretos",$B$394="Manutenção pós-obra",OR($B$396="rs",$B$396="pct_vgv",$B$396="pct_recebido")),AND($B$393="diretos",$B$394="Outro",OR($B$396="rs",$B$396="pct_vgv",$B$396="pct_recebido")),AND($B$393="indireto",$B$394="Marketing global",OR($B$396="rs",$B$396="pct_vgv",$B$396="pct_recebido")),AND($B$393="indireto",$B$394="Stand de vendas",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="indireto",$B$394="Gestão",OR($B$396="rs",$B$396="pct_vgv",$B$396="pct_recebido")),AND($B$393="indireto",$B$394="Outro",OR($B$396="rs",$B$396="pct_vgv",$B$396="pct_recebido")),AND($B$393="financeiro",$B$394="Juros de financiamento",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="financeiro",$B$394="Taxas bancárias",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="financeiro",$B$394="Estruturação de dívida",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="financeiro",$B$394="Investidores",OR($B$396="rs",$B$396="pct_vgv")),AND($B$393="financeiro",$B$394="Outro",OR($B$396="rs",$B$396="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$397&lt;&gt;"",$B$398&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$396,3)="pct",$B$398="",$B$397=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C881" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D881" s="22" t="inlineStr">
@@ -16457,16 +16457,16 @@
     <row r="882">
       <c r="A882" s="19" t="inlineStr">
         <is>
-          <t>Permuta física 2 — VGV entregue (unidades × área × preço sugerido)</t>
-        </is>
-      </c>
-      <c r="B882" s="25">
-        <f>IF($B$637="",0,N($B$638)*(($B$59=$B$637)*(N($B$61)+N($B$62))*N($B$66)+($B$68=$B$637)*(N($B$70)+N($B$71))*N($B$75)+($B$77=$B$637)*(N($B$79)+N($B$80))*N($B$84)+($B$86=$B$637)*(N($B$88)+N($B$89))*N($B$93)+($B$95=$B$637)*(N($B$97)+N($B$98))*N($B$102)+($B$104=$B$637)*(N($B$106)+N($B$107))*N($B$111)+($B$113=$B$637)*(N($B$115)+N($B$116))*N($B$120)+($B$122=$B$637)*(N($B$124)+N($B$125))*N($B$129)+($B$131=$B$637)*(N($B$133)+N($B$134))*N($B$138)+($B$140=$B$637)*(N($B$142)+N($B$143))*N($B$147)))</f>
+          <t>Custo 8 — conferência</t>
+        </is>
+      </c>
+      <c r="B882" s="24">
+        <f>IF(AND($B$404="",$B$405=""),"",IF(OR($B$404="",$B$405="",$B$407=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$404="terreno",$B$405="Preço",OR($B$407="rs",$B$407="rs_m2_terreno")),AND($B$404="terreno",$B$405="Registro",OR($B$407="rs",$B$407="rs_m2_priv")),AND($B$404="terreno",$B$405="Outro",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="obra",$B$405="Construção",OR($B$407="rs",$B$407="rs_m2_priv")),AND($B$404="obra",$B$405="Outorga",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="obra",$B$405="Decoração",OR($B$407="rs",$B$407="rs_m2_priv")),AND($B$404="obra",$B$405="Gestão da obra",OR($B$407="rs",$B$407="pct_obra")),AND($B$404="obra",$B$405="Contingência",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="obra",$B$405="Outro",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="diretos",$B$405="Marketing &amp; Publicidade",OR($B$407="rs",$B$407="pct_vgv",$B$407="pct_recebido")),AND($B$404="diretos",$B$405="Corretagem de vendas",OR($B$407="pct_vgv")),AND($B$404="diretos",$B$405="Projetos",OR($B$407="rs",$B$407="rs_m2_priv",$B$407="pct_constr")),AND($B$404="diretos",$B$405="Licenças e Aprovações",OR($B$407="rs",$B$407="rs_m2_priv")),AND($B$404="diretos",$B$405="Manutenção pós-obra",OR($B$407="rs",$B$407="pct_vgv",$B$407="pct_recebido")),AND($B$404="diretos",$B$405="Outro",OR($B$407="rs",$B$407="pct_vgv",$B$407="pct_recebido")),AND($B$404="indireto",$B$405="Marketing global",OR($B$407="rs",$B$407="pct_vgv",$B$407="pct_recebido")),AND($B$404="indireto",$B$405="Stand de vendas",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="indireto",$B$405="Gestão",OR($B$407="rs",$B$407="pct_vgv",$B$407="pct_recebido")),AND($B$404="indireto",$B$405="Outro",OR($B$407="rs",$B$407="pct_vgv",$B$407="pct_recebido")),AND($B$404="financeiro",$B$405="Juros de financiamento",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="financeiro",$B$405="Taxas bancárias",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="financeiro",$B$405="Estruturação de dívida",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="financeiro",$B$405="Investidores",OR($B$407="rs",$B$407="pct_vgv")),AND($B$404="financeiro",$B$405="Outro",OR($B$407="rs",$B$407="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$408&lt;&gt;"",$B$409&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$407,3)="pct",$B$409="",$B$408=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C882" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D882" s="22" t="inlineStr">
@@ -16478,16 +16478,16 @@
     <row r="883">
       <c r="A883" s="19" t="inlineStr">
         <is>
-          <t>Permuta financeira 2 — equivalente em R$</t>
-        </is>
-      </c>
-      <c r="B883" s="25">
-        <f>IF($B$645="pct_vgv",N($B$647)*$B$788,IF($B$645="rs",N($B$646),0))</f>
+          <t>Custo 9 — conferência</t>
+        </is>
+      </c>
+      <c r="B883" s="24">
+        <f>IF(AND($B$415="",$B$416=""),"",IF(OR($B$415="",$B$416="",$B$418=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$415="terreno",$B$416="Preço",OR($B$418="rs",$B$418="rs_m2_terreno")),AND($B$415="terreno",$B$416="Registro",OR($B$418="rs",$B$418="rs_m2_priv")),AND($B$415="terreno",$B$416="Outro",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="obra",$B$416="Construção",OR($B$418="rs",$B$418="rs_m2_priv")),AND($B$415="obra",$B$416="Outorga",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="obra",$B$416="Decoração",OR($B$418="rs",$B$418="rs_m2_priv")),AND($B$415="obra",$B$416="Gestão da obra",OR($B$418="rs",$B$418="pct_obra")),AND($B$415="obra",$B$416="Contingência",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="obra",$B$416="Outro",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="diretos",$B$416="Marketing &amp; Publicidade",OR($B$418="rs",$B$418="pct_vgv",$B$418="pct_recebido")),AND($B$415="diretos",$B$416="Corretagem de vendas",OR($B$418="pct_vgv")),AND($B$415="diretos",$B$416="Projetos",OR($B$418="rs",$B$418="rs_m2_priv",$B$418="pct_constr")),AND($B$415="diretos",$B$416="Licenças e Aprovações",OR($B$418="rs",$B$418="rs_m2_priv")),AND($B$415="diretos",$B$416="Manutenção pós-obra",OR($B$418="rs",$B$418="pct_vgv",$B$418="pct_recebido")),AND($B$415="diretos",$B$416="Outro",OR($B$418="rs",$B$418="pct_vgv",$B$418="pct_recebido")),AND($B$415="indireto",$B$416="Marketing global",OR($B$418="rs",$B$418="pct_vgv",$B$418="pct_recebido")),AND($B$415="indireto",$B$416="Stand de vendas",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="indireto",$B$416="Gestão",OR($B$418="rs",$B$418="pct_vgv",$B$418="pct_recebido")),AND($B$415="indireto",$B$416="Outro",OR($B$418="rs",$B$418="pct_vgv",$B$418="pct_recebido")),AND($B$415="financeiro",$B$416="Juros de financiamento",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="financeiro",$B$416="Taxas bancárias",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="financeiro",$B$416="Estruturação de dívida",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="financeiro",$B$416="Investidores",OR($B$418="rs",$B$418="pct_vgv")),AND($B$415="financeiro",$B$416="Outro",OR($B$418="rs",$B$418="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$419&lt;&gt;"",$B$420&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$418,3)="pct",$B$420="",$B$419=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C883" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D883" s="22" t="inlineStr">
@@ -16499,16 +16499,16 @@
     <row r="884">
       <c r="A884" s="19" t="inlineStr">
         <is>
-          <t>Σ valor das dívidas</t>
-        </is>
-      </c>
-      <c r="B884" s="25">
-        <f>N($B$662)+N($B$675)+N($B$688)</f>
+          <t>Custo 10 — conferência</t>
+        </is>
+      </c>
+      <c r="B884" s="24">
+        <f>IF(AND($B$426="",$B$427=""),"",IF(OR($B$426="",$B$427="",$B$429=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$426="terreno",$B$427="Preço",OR($B$429="rs",$B$429="rs_m2_terreno")),AND($B$426="terreno",$B$427="Registro",OR($B$429="rs",$B$429="rs_m2_priv")),AND($B$426="terreno",$B$427="Outro",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="obra",$B$427="Construção",OR($B$429="rs",$B$429="rs_m2_priv")),AND($B$426="obra",$B$427="Outorga",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="obra",$B$427="Decoração",OR($B$429="rs",$B$429="rs_m2_priv")),AND($B$426="obra",$B$427="Gestão da obra",OR($B$429="rs",$B$429="pct_obra")),AND($B$426="obra",$B$427="Contingência",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="obra",$B$427="Outro",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="diretos",$B$427="Marketing &amp; Publicidade",OR($B$429="rs",$B$429="pct_vgv",$B$429="pct_recebido")),AND($B$426="diretos",$B$427="Corretagem de vendas",OR($B$429="pct_vgv")),AND($B$426="diretos",$B$427="Projetos",OR($B$429="rs",$B$429="rs_m2_priv",$B$429="pct_constr")),AND($B$426="diretos",$B$427="Licenças e Aprovações",OR($B$429="rs",$B$429="rs_m2_priv")),AND($B$426="diretos",$B$427="Manutenção pós-obra",OR($B$429="rs",$B$429="pct_vgv",$B$429="pct_recebido")),AND($B$426="diretos",$B$427="Outro",OR($B$429="rs",$B$429="pct_vgv",$B$429="pct_recebido")),AND($B$426="indireto",$B$427="Marketing global",OR($B$429="rs",$B$429="pct_vgv",$B$429="pct_recebido")),AND($B$426="indireto",$B$427="Stand de vendas",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="indireto",$B$427="Gestão",OR($B$429="rs",$B$429="pct_vgv",$B$429="pct_recebido")),AND($B$426="indireto",$B$427="Outro",OR($B$429="rs",$B$429="pct_vgv",$B$429="pct_recebido")),AND($B$426="financeiro",$B$427="Juros de financiamento",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="financeiro",$B$427="Taxas bancárias",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="financeiro",$B$427="Estruturação de dívida",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="financeiro",$B$427="Investidores",OR($B$429="rs",$B$429="pct_vgv")),AND($B$426="financeiro",$B$427="Outro",OR($B$429="rs",$B$429="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$430&lt;&gt;"",$B$431&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$429,3)="pct",$B$431="",$B$430=""),"⚠ falta o valor na linha certa","OK")))))</f>
         <v/>
       </c>
       <c r="C884" s="21" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>alerta</t>
         </is>
       </c>
       <c r="D884" s="22" t="inlineStr">
@@ -16520,203 +16520,840 @@
     <row r="885">
       <c r="A885" s="19" t="inlineStr">
         <is>
+          <t>Custo 11 — conferência</t>
+        </is>
+      </c>
+      <c r="B885" s="24">
+        <f>IF(AND($B$437="",$B$438=""),"",IF(OR($B$437="",$B$438="",$B$440=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$437="terreno",$B$438="Preço",OR($B$440="rs",$B$440="rs_m2_terreno")),AND($B$437="terreno",$B$438="Registro",OR($B$440="rs",$B$440="rs_m2_priv")),AND($B$437="terreno",$B$438="Outro",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="obra",$B$438="Construção",OR($B$440="rs",$B$440="rs_m2_priv")),AND($B$437="obra",$B$438="Outorga",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="obra",$B$438="Decoração",OR($B$440="rs",$B$440="rs_m2_priv")),AND($B$437="obra",$B$438="Gestão da obra",OR($B$440="rs",$B$440="pct_obra")),AND($B$437="obra",$B$438="Contingência",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="obra",$B$438="Outro",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="diretos",$B$438="Marketing &amp; Publicidade",OR($B$440="rs",$B$440="pct_vgv",$B$440="pct_recebido")),AND($B$437="diretos",$B$438="Corretagem de vendas",OR($B$440="pct_vgv")),AND($B$437="diretos",$B$438="Projetos",OR($B$440="rs",$B$440="rs_m2_priv",$B$440="pct_constr")),AND($B$437="diretos",$B$438="Licenças e Aprovações",OR($B$440="rs",$B$440="rs_m2_priv")),AND($B$437="diretos",$B$438="Manutenção pós-obra",OR($B$440="rs",$B$440="pct_vgv",$B$440="pct_recebido")),AND($B$437="diretos",$B$438="Outro",OR($B$440="rs",$B$440="pct_vgv",$B$440="pct_recebido")),AND($B$437="indireto",$B$438="Marketing global",OR($B$440="rs",$B$440="pct_vgv",$B$440="pct_recebido")),AND($B$437="indireto",$B$438="Stand de vendas",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="indireto",$B$438="Gestão",OR($B$440="rs",$B$440="pct_vgv",$B$440="pct_recebido")),AND($B$437="indireto",$B$438="Outro",OR($B$440="rs",$B$440="pct_vgv",$B$440="pct_recebido")),AND($B$437="financeiro",$B$438="Juros de financiamento",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="financeiro",$B$438="Taxas bancárias",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="financeiro",$B$438="Estruturação de dívida",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="financeiro",$B$438="Investidores",OR($B$440="rs",$B$440="pct_vgv")),AND($B$437="financeiro",$B$438="Outro",OR($B$440="rs",$B$440="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$441&lt;&gt;"",$B$442&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$440,3)="pct",$B$442="",$B$441=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C885" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D885" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="19" t="inlineStr">
+        <is>
+          <t>Custo 12 — conferência</t>
+        </is>
+      </c>
+      <c r="B886" s="24">
+        <f>IF(AND($B$448="",$B$449=""),"",IF(OR($B$448="",$B$449="",$B$451=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$448="terreno",$B$449="Preço",OR($B$451="rs",$B$451="rs_m2_terreno")),AND($B$448="terreno",$B$449="Registro",OR($B$451="rs",$B$451="rs_m2_priv")),AND($B$448="terreno",$B$449="Outro",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="obra",$B$449="Construção",OR($B$451="rs",$B$451="rs_m2_priv")),AND($B$448="obra",$B$449="Outorga",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="obra",$B$449="Decoração",OR($B$451="rs",$B$451="rs_m2_priv")),AND($B$448="obra",$B$449="Gestão da obra",OR($B$451="rs",$B$451="pct_obra")),AND($B$448="obra",$B$449="Contingência",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="obra",$B$449="Outro",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="diretos",$B$449="Marketing &amp; Publicidade",OR($B$451="rs",$B$451="pct_vgv",$B$451="pct_recebido")),AND($B$448="diretos",$B$449="Corretagem de vendas",OR($B$451="pct_vgv")),AND($B$448="diretos",$B$449="Projetos",OR($B$451="rs",$B$451="rs_m2_priv",$B$451="pct_constr")),AND($B$448="diretos",$B$449="Licenças e Aprovações",OR($B$451="rs",$B$451="rs_m2_priv")),AND($B$448="diretos",$B$449="Manutenção pós-obra",OR($B$451="rs",$B$451="pct_vgv",$B$451="pct_recebido")),AND($B$448="diretos",$B$449="Outro",OR($B$451="rs",$B$451="pct_vgv",$B$451="pct_recebido")),AND($B$448="indireto",$B$449="Marketing global",OR($B$451="rs",$B$451="pct_vgv",$B$451="pct_recebido")),AND($B$448="indireto",$B$449="Stand de vendas",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="indireto",$B$449="Gestão",OR($B$451="rs",$B$451="pct_vgv",$B$451="pct_recebido")),AND($B$448="indireto",$B$449="Outro",OR($B$451="rs",$B$451="pct_vgv",$B$451="pct_recebido")),AND($B$448="financeiro",$B$449="Juros de financiamento",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="financeiro",$B$449="Taxas bancárias",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="financeiro",$B$449="Estruturação de dívida",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="financeiro",$B$449="Investidores",OR($B$451="rs",$B$451="pct_vgv")),AND($B$448="financeiro",$B$449="Outro",OR($B$451="rs",$B$451="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$452&lt;&gt;"",$B$453&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$451,3)="pct",$B$453="",$B$452=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C886" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D886" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="19" t="inlineStr">
+        <is>
+          <t>Custo 13 — conferência</t>
+        </is>
+      </c>
+      <c r="B887" s="24">
+        <f>IF(AND($B$459="",$B$460=""),"",IF(OR($B$459="",$B$460="",$B$462=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$459="terreno",$B$460="Preço",OR($B$462="rs",$B$462="rs_m2_terreno")),AND($B$459="terreno",$B$460="Registro",OR($B$462="rs",$B$462="rs_m2_priv")),AND($B$459="terreno",$B$460="Outro",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="obra",$B$460="Construção",OR($B$462="rs",$B$462="rs_m2_priv")),AND($B$459="obra",$B$460="Outorga",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="obra",$B$460="Decoração",OR($B$462="rs",$B$462="rs_m2_priv")),AND($B$459="obra",$B$460="Gestão da obra",OR($B$462="rs",$B$462="pct_obra")),AND($B$459="obra",$B$460="Contingência",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="obra",$B$460="Outro",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="diretos",$B$460="Marketing &amp; Publicidade",OR($B$462="rs",$B$462="pct_vgv",$B$462="pct_recebido")),AND($B$459="diretos",$B$460="Corretagem de vendas",OR($B$462="pct_vgv")),AND($B$459="diretos",$B$460="Projetos",OR($B$462="rs",$B$462="rs_m2_priv",$B$462="pct_constr")),AND($B$459="diretos",$B$460="Licenças e Aprovações",OR($B$462="rs",$B$462="rs_m2_priv")),AND($B$459="diretos",$B$460="Manutenção pós-obra",OR($B$462="rs",$B$462="pct_vgv",$B$462="pct_recebido")),AND($B$459="diretos",$B$460="Outro",OR($B$462="rs",$B$462="pct_vgv",$B$462="pct_recebido")),AND($B$459="indireto",$B$460="Marketing global",OR($B$462="rs",$B$462="pct_vgv",$B$462="pct_recebido")),AND($B$459="indireto",$B$460="Stand de vendas",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="indireto",$B$460="Gestão",OR($B$462="rs",$B$462="pct_vgv",$B$462="pct_recebido")),AND($B$459="indireto",$B$460="Outro",OR($B$462="rs",$B$462="pct_vgv",$B$462="pct_recebido")),AND($B$459="financeiro",$B$460="Juros de financiamento",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="financeiro",$B$460="Taxas bancárias",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="financeiro",$B$460="Estruturação de dívida",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="financeiro",$B$460="Investidores",OR($B$462="rs",$B$462="pct_vgv")),AND($B$459="financeiro",$B$460="Outro",OR($B$462="rs",$B$462="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$463&lt;&gt;"",$B$464&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$462,3)="pct",$B$464="",$B$463=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C887" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D887" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="19" t="inlineStr">
+        <is>
+          <t>Custo 14 — conferência</t>
+        </is>
+      </c>
+      <c r="B888" s="24">
+        <f>IF(AND($B$470="",$B$471=""),"",IF(OR($B$470="",$B$471="",$B$473=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$470="terreno",$B$471="Preço",OR($B$473="rs",$B$473="rs_m2_terreno")),AND($B$470="terreno",$B$471="Registro",OR($B$473="rs",$B$473="rs_m2_priv")),AND($B$470="terreno",$B$471="Outro",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="obra",$B$471="Construção",OR($B$473="rs",$B$473="rs_m2_priv")),AND($B$470="obra",$B$471="Outorga",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="obra",$B$471="Decoração",OR($B$473="rs",$B$473="rs_m2_priv")),AND($B$470="obra",$B$471="Gestão da obra",OR($B$473="rs",$B$473="pct_obra")),AND($B$470="obra",$B$471="Contingência",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="obra",$B$471="Outro",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="diretos",$B$471="Marketing &amp; Publicidade",OR($B$473="rs",$B$473="pct_vgv",$B$473="pct_recebido")),AND($B$470="diretos",$B$471="Corretagem de vendas",OR($B$473="pct_vgv")),AND($B$470="diretos",$B$471="Projetos",OR($B$473="rs",$B$473="rs_m2_priv",$B$473="pct_constr")),AND($B$470="diretos",$B$471="Licenças e Aprovações",OR($B$473="rs",$B$473="rs_m2_priv")),AND($B$470="diretos",$B$471="Manutenção pós-obra",OR($B$473="rs",$B$473="pct_vgv",$B$473="pct_recebido")),AND($B$470="diretos",$B$471="Outro",OR($B$473="rs",$B$473="pct_vgv",$B$473="pct_recebido")),AND($B$470="indireto",$B$471="Marketing global",OR($B$473="rs",$B$473="pct_vgv",$B$473="pct_recebido")),AND($B$470="indireto",$B$471="Stand de vendas",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="indireto",$B$471="Gestão",OR($B$473="rs",$B$473="pct_vgv",$B$473="pct_recebido")),AND($B$470="indireto",$B$471="Outro",OR($B$473="rs",$B$473="pct_vgv",$B$473="pct_recebido")),AND($B$470="financeiro",$B$471="Juros de financiamento",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="financeiro",$B$471="Taxas bancárias",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="financeiro",$B$471="Estruturação de dívida",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="financeiro",$B$471="Investidores",OR($B$473="rs",$B$473="pct_vgv")),AND($B$470="financeiro",$B$471="Outro",OR($B$473="rs",$B$473="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$474&lt;&gt;"",$B$475&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$473,3)="pct",$B$475="",$B$474=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C888" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D888" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="19" t="inlineStr">
+        <is>
+          <t>Custo 15 — conferência</t>
+        </is>
+      </c>
+      <c r="B889" s="24">
+        <f>IF(AND($B$481="",$B$482=""),"",IF(OR($B$481="",$B$482="",$B$484=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$481="terreno",$B$482="Preço",OR($B$484="rs",$B$484="rs_m2_terreno")),AND($B$481="terreno",$B$482="Registro",OR($B$484="rs",$B$484="rs_m2_priv")),AND($B$481="terreno",$B$482="Outro",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="obra",$B$482="Construção",OR($B$484="rs",$B$484="rs_m2_priv")),AND($B$481="obra",$B$482="Outorga",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="obra",$B$482="Decoração",OR($B$484="rs",$B$484="rs_m2_priv")),AND($B$481="obra",$B$482="Gestão da obra",OR($B$484="rs",$B$484="pct_obra")),AND($B$481="obra",$B$482="Contingência",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="obra",$B$482="Outro",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="diretos",$B$482="Marketing &amp; Publicidade",OR($B$484="rs",$B$484="pct_vgv",$B$484="pct_recebido")),AND($B$481="diretos",$B$482="Corretagem de vendas",OR($B$484="pct_vgv")),AND($B$481="diretos",$B$482="Projetos",OR($B$484="rs",$B$484="rs_m2_priv",$B$484="pct_constr")),AND($B$481="diretos",$B$482="Licenças e Aprovações",OR($B$484="rs",$B$484="rs_m2_priv")),AND($B$481="diretos",$B$482="Manutenção pós-obra",OR($B$484="rs",$B$484="pct_vgv",$B$484="pct_recebido")),AND($B$481="diretos",$B$482="Outro",OR($B$484="rs",$B$484="pct_vgv",$B$484="pct_recebido")),AND($B$481="indireto",$B$482="Marketing global",OR($B$484="rs",$B$484="pct_vgv",$B$484="pct_recebido")),AND($B$481="indireto",$B$482="Stand de vendas",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="indireto",$B$482="Gestão",OR($B$484="rs",$B$484="pct_vgv",$B$484="pct_recebido")),AND($B$481="indireto",$B$482="Outro",OR($B$484="rs",$B$484="pct_vgv",$B$484="pct_recebido")),AND($B$481="financeiro",$B$482="Juros de financiamento",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="financeiro",$B$482="Taxas bancárias",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="financeiro",$B$482="Estruturação de dívida",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="financeiro",$B$482="Investidores",OR($B$484="rs",$B$484="pct_vgv")),AND($B$481="financeiro",$B$482="Outro",OR($B$484="rs",$B$484="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$485&lt;&gt;"",$B$486&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$484,3)="pct",$B$486="",$B$485=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C889" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D889" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="19" t="inlineStr">
+        <is>
+          <t>Custo 16 — conferência</t>
+        </is>
+      </c>
+      <c r="B890" s="24">
+        <f>IF(AND($B$492="",$B$493=""),"",IF(OR($B$492="",$B$493="",$B$495=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$492="terreno",$B$493="Preço",OR($B$495="rs",$B$495="rs_m2_terreno")),AND($B$492="terreno",$B$493="Registro",OR($B$495="rs",$B$495="rs_m2_priv")),AND($B$492="terreno",$B$493="Outro",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="obra",$B$493="Construção",OR($B$495="rs",$B$495="rs_m2_priv")),AND($B$492="obra",$B$493="Outorga",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="obra",$B$493="Decoração",OR($B$495="rs",$B$495="rs_m2_priv")),AND($B$492="obra",$B$493="Gestão da obra",OR($B$495="rs",$B$495="pct_obra")),AND($B$492="obra",$B$493="Contingência",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="obra",$B$493="Outro",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="diretos",$B$493="Marketing &amp; Publicidade",OR($B$495="rs",$B$495="pct_vgv",$B$495="pct_recebido")),AND($B$492="diretos",$B$493="Corretagem de vendas",OR($B$495="pct_vgv")),AND($B$492="diretos",$B$493="Projetos",OR($B$495="rs",$B$495="rs_m2_priv",$B$495="pct_constr")),AND($B$492="diretos",$B$493="Licenças e Aprovações",OR($B$495="rs",$B$495="rs_m2_priv")),AND($B$492="diretos",$B$493="Manutenção pós-obra",OR($B$495="rs",$B$495="pct_vgv",$B$495="pct_recebido")),AND($B$492="diretos",$B$493="Outro",OR($B$495="rs",$B$495="pct_vgv",$B$495="pct_recebido")),AND($B$492="indireto",$B$493="Marketing global",OR($B$495="rs",$B$495="pct_vgv",$B$495="pct_recebido")),AND($B$492="indireto",$B$493="Stand de vendas",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="indireto",$B$493="Gestão",OR($B$495="rs",$B$495="pct_vgv",$B$495="pct_recebido")),AND($B$492="indireto",$B$493="Outro",OR($B$495="rs",$B$495="pct_vgv",$B$495="pct_recebido")),AND($B$492="financeiro",$B$493="Juros de financiamento",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="financeiro",$B$493="Taxas bancárias",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="financeiro",$B$493="Estruturação de dívida",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="financeiro",$B$493="Investidores",OR($B$495="rs",$B$495="pct_vgv")),AND($B$492="financeiro",$B$493="Outro",OR($B$495="rs",$B$495="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$496&lt;&gt;"",$B$497&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$495,3)="pct",$B$497="",$B$496=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C890" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D890" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="19" t="inlineStr">
+        <is>
+          <t>Custo 17 — conferência</t>
+        </is>
+      </c>
+      <c r="B891" s="24">
+        <f>IF(AND($B$503="",$B$504=""),"",IF(OR($B$503="",$B$504="",$B$506=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$503="terreno",$B$504="Preço",OR($B$506="rs",$B$506="rs_m2_terreno")),AND($B$503="terreno",$B$504="Registro",OR($B$506="rs",$B$506="rs_m2_priv")),AND($B$503="terreno",$B$504="Outro",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="obra",$B$504="Construção",OR($B$506="rs",$B$506="rs_m2_priv")),AND($B$503="obra",$B$504="Outorga",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="obra",$B$504="Decoração",OR($B$506="rs",$B$506="rs_m2_priv")),AND($B$503="obra",$B$504="Gestão da obra",OR($B$506="rs",$B$506="pct_obra")),AND($B$503="obra",$B$504="Contingência",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="obra",$B$504="Outro",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="diretos",$B$504="Marketing &amp; Publicidade",OR($B$506="rs",$B$506="pct_vgv",$B$506="pct_recebido")),AND($B$503="diretos",$B$504="Corretagem de vendas",OR($B$506="pct_vgv")),AND($B$503="diretos",$B$504="Projetos",OR($B$506="rs",$B$506="rs_m2_priv",$B$506="pct_constr")),AND($B$503="diretos",$B$504="Licenças e Aprovações",OR($B$506="rs",$B$506="rs_m2_priv")),AND($B$503="diretos",$B$504="Manutenção pós-obra",OR($B$506="rs",$B$506="pct_vgv",$B$506="pct_recebido")),AND($B$503="diretos",$B$504="Outro",OR($B$506="rs",$B$506="pct_vgv",$B$506="pct_recebido")),AND($B$503="indireto",$B$504="Marketing global",OR($B$506="rs",$B$506="pct_vgv",$B$506="pct_recebido")),AND($B$503="indireto",$B$504="Stand de vendas",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="indireto",$B$504="Gestão",OR($B$506="rs",$B$506="pct_vgv",$B$506="pct_recebido")),AND($B$503="indireto",$B$504="Outro",OR($B$506="rs",$B$506="pct_vgv",$B$506="pct_recebido")),AND($B$503="financeiro",$B$504="Juros de financiamento",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="financeiro",$B$504="Taxas bancárias",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="financeiro",$B$504="Estruturação de dívida",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="financeiro",$B$504="Investidores",OR($B$506="rs",$B$506="pct_vgv")),AND($B$503="financeiro",$B$504="Outro",OR($B$506="rs",$B$506="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$507&lt;&gt;"",$B$508&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$506,3)="pct",$B$508="",$B$507=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C891" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D891" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="19" t="inlineStr">
+        <is>
+          <t>Custo 18 — conferência</t>
+        </is>
+      </c>
+      <c r="B892" s="24">
+        <f>IF(AND($B$514="",$B$515=""),"",IF(OR($B$514="",$B$515="",$B$517=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$514="terreno",$B$515="Preço",OR($B$517="rs",$B$517="rs_m2_terreno")),AND($B$514="terreno",$B$515="Registro",OR($B$517="rs",$B$517="rs_m2_priv")),AND($B$514="terreno",$B$515="Outro",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="obra",$B$515="Construção",OR($B$517="rs",$B$517="rs_m2_priv")),AND($B$514="obra",$B$515="Outorga",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="obra",$B$515="Decoração",OR($B$517="rs",$B$517="rs_m2_priv")),AND($B$514="obra",$B$515="Gestão da obra",OR($B$517="rs",$B$517="pct_obra")),AND($B$514="obra",$B$515="Contingência",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="obra",$B$515="Outro",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="diretos",$B$515="Marketing &amp; Publicidade",OR($B$517="rs",$B$517="pct_vgv",$B$517="pct_recebido")),AND($B$514="diretos",$B$515="Corretagem de vendas",OR($B$517="pct_vgv")),AND($B$514="diretos",$B$515="Projetos",OR($B$517="rs",$B$517="rs_m2_priv",$B$517="pct_constr")),AND($B$514="diretos",$B$515="Licenças e Aprovações",OR($B$517="rs",$B$517="rs_m2_priv")),AND($B$514="diretos",$B$515="Manutenção pós-obra",OR($B$517="rs",$B$517="pct_vgv",$B$517="pct_recebido")),AND($B$514="diretos",$B$515="Outro",OR($B$517="rs",$B$517="pct_vgv",$B$517="pct_recebido")),AND($B$514="indireto",$B$515="Marketing global",OR($B$517="rs",$B$517="pct_vgv",$B$517="pct_recebido")),AND($B$514="indireto",$B$515="Stand de vendas",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="indireto",$B$515="Gestão",OR($B$517="rs",$B$517="pct_vgv",$B$517="pct_recebido")),AND($B$514="indireto",$B$515="Outro",OR($B$517="rs",$B$517="pct_vgv",$B$517="pct_recebido")),AND($B$514="financeiro",$B$515="Juros de financiamento",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="financeiro",$B$515="Taxas bancárias",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="financeiro",$B$515="Estruturação de dívida",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="financeiro",$B$515="Investidores",OR($B$517="rs",$B$517="pct_vgv")),AND($B$514="financeiro",$B$515="Outro",OR($B$517="rs",$B$517="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$518&lt;&gt;"",$B$519&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$517,3)="pct",$B$519="",$B$518=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C892" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D892" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="19" t="inlineStr">
+        <is>
+          <t>Custo 19 — conferência</t>
+        </is>
+      </c>
+      <c r="B893" s="24">
+        <f>IF(AND($B$525="",$B$526=""),"",IF(OR($B$525="",$B$526="",$B$528=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$525="terreno",$B$526="Preço",OR($B$528="rs",$B$528="rs_m2_terreno")),AND($B$525="terreno",$B$526="Registro",OR($B$528="rs",$B$528="rs_m2_priv")),AND($B$525="terreno",$B$526="Outro",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="obra",$B$526="Construção",OR($B$528="rs",$B$528="rs_m2_priv")),AND($B$525="obra",$B$526="Outorga",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="obra",$B$526="Decoração",OR($B$528="rs",$B$528="rs_m2_priv")),AND($B$525="obra",$B$526="Gestão da obra",OR($B$528="rs",$B$528="pct_obra")),AND($B$525="obra",$B$526="Contingência",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="obra",$B$526="Outro",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="diretos",$B$526="Marketing &amp; Publicidade",OR($B$528="rs",$B$528="pct_vgv",$B$528="pct_recebido")),AND($B$525="diretos",$B$526="Corretagem de vendas",OR($B$528="pct_vgv")),AND($B$525="diretos",$B$526="Projetos",OR($B$528="rs",$B$528="rs_m2_priv",$B$528="pct_constr")),AND($B$525="diretos",$B$526="Licenças e Aprovações",OR($B$528="rs",$B$528="rs_m2_priv")),AND($B$525="diretos",$B$526="Manutenção pós-obra",OR($B$528="rs",$B$528="pct_vgv",$B$528="pct_recebido")),AND($B$525="diretos",$B$526="Outro",OR($B$528="rs",$B$528="pct_vgv",$B$528="pct_recebido")),AND($B$525="indireto",$B$526="Marketing global",OR($B$528="rs",$B$528="pct_vgv",$B$528="pct_recebido")),AND($B$525="indireto",$B$526="Stand de vendas",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="indireto",$B$526="Gestão",OR($B$528="rs",$B$528="pct_vgv",$B$528="pct_recebido")),AND($B$525="indireto",$B$526="Outro",OR($B$528="rs",$B$528="pct_vgv",$B$528="pct_recebido")),AND($B$525="financeiro",$B$526="Juros de financiamento",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="financeiro",$B$526="Taxas bancárias",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="financeiro",$B$526="Estruturação de dívida",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="financeiro",$B$526="Investidores",OR($B$528="rs",$B$528="pct_vgv")),AND($B$525="financeiro",$B$526="Outro",OR($B$528="rs",$B$528="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$529&lt;&gt;"",$B$530&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$528,3)="pct",$B$530="",$B$529=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C893" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D893" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="19" t="inlineStr">
+        <is>
+          <t>Custo 20 — conferência</t>
+        </is>
+      </c>
+      <c r="B894" s="24">
+        <f>IF(AND($B$536="",$B$537=""),"",IF(OR($B$536="",$B$537="",$B$539=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$536="terreno",$B$537="Preço",OR($B$539="rs",$B$539="rs_m2_terreno")),AND($B$536="terreno",$B$537="Registro",OR($B$539="rs",$B$539="rs_m2_priv")),AND($B$536="terreno",$B$537="Outro",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="obra",$B$537="Construção",OR($B$539="rs",$B$539="rs_m2_priv")),AND($B$536="obra",$B$537="Outorga",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="obra",$B$537="Decoração",OR($B$539="rs",$B$539="rs_m2_priv")),AND($B$536="obra",$B$537="Gestão da obra",OR($B$539="rs",$B$539="pct_obra")),AND($B$536="obra",$B$537="Contingência",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="obra",$B$537="Outro",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="diretos",$B$537="Marketing &amp; Publicidade",OR($B$539="rs",$B$539="pct_vgv",$B$539="pct_recebido")),AND($B$536="diretos",$B$537="Corretagem de vendas",OR($B$539="pct_vgv")),AND($B$536="diretos",$B$537="Projetos",OR($B$539="rs",$B$539="rs_m2_priv",$B$539="pct_constr")),AND($B$536="diretos",$B$537="Licenças e Aprovações",OR($B$539="rs",$B$539="rs_m2_priv")),AND($B$536="diretos",$B$537="Manutenção pós-obra",OR($B$539="rs",$B$539="pct_vgv",$B$539="pct_recebido")),AND($B$536="diretos",$B$537="Outro",OR($B$539="rs",$B$539="pct_vgv",$B$539="pct_recebido")),AND($B$536="indireto",$B$537="Marketing global",OR($B$539="rs",$B$539="pct_vgv",$B$539="pct_recebido")),AND($B$536="indireto",$B$537="Stand de vendas",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="indireto",$B$537="Gestão",OR($B$539="rs",$B$539="pct_vgv",$B$539="pct_recebido")),AND($B$536="indireto",$B$537="Outro",OR($B$539="rs",$B$539="pct_vgv",$B$539="pct_recebido")),AND($B$536="financeiro",$B$537="Juros de financiamento",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="financeiro",$B$537="Taxas bancárias",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="financeiro",$B$537="Estruturação de dívida",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="financeiro",$B$537="Investidores",OR($B$539="rs",$B$539="pct_vgv")),AND($B$536="financeiro",$B$537="Outro",OR($B$539="rs",$B$539="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$540&lt;&gt;"",$B$541&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$539,3)="pct",$B$541="",$B$540=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C894" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D894" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="19" t="inlineStr">
+        <is>
+          <t>Custo 21 — conferência</t>
+        </is>
+      </c>
+      <c r="B895" s="24">
+        <f>IF(AND($B$547="",$B$548=""),"",IF(OR($B$547="",$B$548="",$B$550=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$547="terreno",$B$548="Preço",OR($B$550="rs",$B$550="rs_m2_terreno")),AND($B$547="terreno",$B$548="Registro",OR($B$550="rs",$B$550="rs_m2_priv")),AND($B$547="terreno",$B$548="Outro",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="obra",$B$548="Construção",OR($B$550="rs",$B$550="rs_m2_priv")),AND($B$547="obra",$B$548="Outorga",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="obra",$B$548="Decoração",OR($B$550="rs",$B$550="rs_m2_priv")),AND($B$547="obra",$B$548="Gestão da obra",OR($B$550="rs",$B$550="pct_obra")),AND($B$547="obra",$B$548="Contingência",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="obra",$B$548="Outro",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="diretos",$B$548="Marketing &amp; Publicidade",OR($B$550="rs",$B$550="pct_vgv",$B$550="pct_recebido")),AND($B$547="diretos",$B$548="Corretagem de vendas",OR($B$550="pct_vgv")),AND($B$547="diretos",$B$548="Projetos",OR($B$550="rs",$B$550="rs_m2_priv",$B$550="pct_constr")),AND($B$547="diretos",$B$548="Licenças e Aprovações",OR($B$550="rs",$B$550="rs_m2_priv")),AND($B$547="diretos",$B$548="Manutenção pós-obra",OR($B$550="rs",$B$550="pct_vgv",$B$550="pct_recebido")),AND($B$547="diretos",$B$548="Outro",OR($B$550="rs",$B$550="pct_vgv",$B$550="pct_recebido")),AND($B$547="indireto",$B$548="Marketing global",OR($B$550="rs",$B$550="pct_vgv",$B$550="pct_recebido")),AND($B$547="indireto",$B$548="Stand de vendas",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="indireto",$B$548="Gestão",OR($B$550="rs",$B$550="pct_vgv",$B$550="pct_recebido")),AND($B$547="indireto",$B$548="Outro",OR($B$550="rs",$B$550="pct_vgv",$B$550="pct_recebido")),AND($B$547="financeiro",$B$548="Juros de financiamento",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="financeiro",$B$548="Taxas bancárias",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="financeiro",$B$548="Estruturação de dívida",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="financeiro",$B$548="Investidores",OR($B$550="rs",$B$550="pct_vgv")),AND($B$547="financeiro",$B$548="Outro",OR($B$550="rs",$B$550="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$551&lt;&gt;"",$B$552&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$550,3)="pct",$B$552="",$B$551=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C895" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D895" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="19" t="inlineStr">
+        <is>
+          <t>Custo 22 — conferência</t>
+        </is>
+      </c>
+      <c r="B896" s="24">
+        <f>IF(AND($B$558="",$B$559=""),"",IF(OR($B$558="",$B$559="",$B$561=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$558="terreno",$B$559="Preço",OR($B$561="rs",$B$561="rs_m2_terreno")),AND($B$558="terreno",$B$559="Registro",OR($B$561="rs",$B$561="rs_m2_priv")),AND($B$558="terreno",$B$559="Outro",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="obra",$B$559="Construção",OR($B$561="rs",$B$561="rs_m2_priv")),AND($B$558="obra",$B$559="Outorga",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="obra",$B$559="Decoração",OR($B$561="rs",$B$561="rs_m2_priv")),AND($B$558="obra",$B$559="Gestão da obra",OR($B$561="rs",$B$561="pct_obra")),AND($B$558="obra",$B$559="Contingência",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="obra",$B$559="Outro",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="diretos",$B$559="Marketing &amp; Publicidade",OR($B$561="rs",$B$561="pct_vgv",$B$561="pct_recebido")),AND($B$558="diretos",$B$559="Corretagem de vendas",OR($B$561="pct_vgv")),AND($B$558="diretos",$B$559="Projetos",OR($B$561="rs",$B$561="rs_m2_priv",$B$561="pct_constr")),AND($B$558="diretos",$B$559="Licenças e Aprovações",OR($B$561="rs",$B$561="rs_m2_priv")),AND($B$558="diretos",$B$559="Manutenção pós-obra",OR($B$561="rs",$B$561="pct_vgv",$B$561="pct_recebido")),AND($B$558="diretos",$B$559="Outro",OR($B$561="rs",$B$561="pct_vgv",$B$561="pct_recebido")),AND($B$558="indireto",$B$559="Marketing global",OR($B$561="rs",$B$561="pct_vgv",$B$561="pct_recebido")),AND($B$558="indireto",$B$559="Stand de vendas",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="indireto",$B$559="Gestão",OR($B$561="rs",$B$561="pct_vgv",$B$561="pct_recebido")),AND($B$558="indireto",$B$559="Outro",OR($B$561="rs",$B$561="pct_vgv",$B$561="pct_recebido")),AND($B$558="financeiro",$B$559="Juros de financiamento",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="financeiro",$B$559="Taxas bancárias",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="financeiro",$B$559="Estruturação de dívida",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="financeiro",$B$559="Investidores",OR($B$561="rs",$B$561="pct_vgv")),AND($B$558="financeiro",$B$559="Outro",OR($B$561="rs",$B$561="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$562&lt;&gt;"",$B$563&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$561,3)="pct",$B$563="",$B$562=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C896" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D896" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="19" t="inlineStr">
+        <is>
+          <t>Custo 23 — conferência</t>
+        </is>
+      </c>
+      <c r="B897" s="24">
+        <f>IF(AND($B$569="",$B$570=""),"",IF(OR($B$569="",$B$570="",$B$572=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$569="terreno",$B$570="Preço",OR($B$572="rs",$B$572="rs_m2_terreno")),AND($B$569="terreno",$B$570="Registro",OR($B$572="rs",$B$572="rs_m2_priv")),AND($B$569="terreno",$B$570="Outro",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="obra",$B$570="Construção",OR($B$572="rs",$B$572="rs_m2_priv")),AND($B$569="obra",$B$570="Outorga",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="obra",$B$570="Decoração",OR($B$572="rs",$B$572="rs_m2_priv")),AND($B$569="obra",$B$570="Gestão da obra",OR($B$572="rs",$B$572="pct_obra")),AND($B$569="obra",$B$570="Contingência",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="obra",$B$570="Outro",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="diretos",$B$570="Marketing &amp; Publicidade",OR($B$572="rs",$B$572="pct_vgv",$B$572="pct_recebido")),AND($B$569="diretos",$B$570="Corretagem de vendas",OR($B$572="pct_vgv")),AND($B$569="diretos",$B$570="Projetos",OR($B$572="rs",$B$572="rs_m2_priv",$B$572="pct_constr")),AND($B$569="diretos",$B$570="Licenças e Aprovações",OR($B$572="rs",$B$572="rs_m2_priv")),AND($B$569="diretos",$B$570="Manutenção pós-obra",OR($B$572="rs",$B$572="pct_vgv",$B$572="pct_recebido")),AND($B$569="diretos",$B$570="Outro",OR($B$572="rs",$B$572="pct_vgv",$B$572="pct_recebido")),AND($B$569="indireto",$B$570="Marketing global",OR($B$572="rs",$B$572="pct_vgv",$B$572="pct_recebido")),AND($B$569="indireto",$B$570="Stand de vendas",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="indireto",$B$570="Gestão",OR($B$572="rs",$B$572="pct_vgv",$B$572="pct_recebido")),AND($B$569="indireto",$B$570="Outro",OR($B$572="rs",$B$572="pct_vgv",$B$572="pct_recebido")),AND($B$569="financeiro",$B$570="Juros de financiamento",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="financeiro",$B$570="Taxas bancárias",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="financeiro",$B$570="Estruturação de dívida",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="financeiro",$B$570="Investidores",OR($B$572="rs",$B$572="pct_vgv")),AND($B$569="financeiro",$B$570="Outro",OR($B$572="rs",$B$572="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$573&lt;&gt;"",$B$574&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$572,3)="pct",$B$574="",$B$573=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C897" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D897" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="19" t="inlineStr">
+        <is>
+          <t>Custo 24 — conferência</t>
+        </is>
+      </c>
+      <c r="B898" s="24">
+        <f>IF(AND($B$580="",$B$581=""),"",IF(OR($B$580="",$B$581="",$B$583=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$580="terreno",$B$581="Preço",OR($B$583="rs",$B$583="rs_m2_terreno")),AND($B$580="terreno",$B$581="Registro",OR($B$583="rs",$B$583="rs_m2_priv")),AND($B$580="terreno",$B$581="Outro",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="obra",$B$581="Construção",OR($B$583="rs",$B$583="rs_m2_priv")),AND($B$580="obra",$B$581="Outorga",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="obra",$B$581="Decoração",OR($B$583="rs",$B$583="rs_m2_priv")),AND($B$580="obra",$B$581="Gestão da obra",OR($B$583="rs",$B$583="pct_obra")),AND($B$580="obra",$B$581="Contingência",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="obra",$B$581="Outro",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="diretos",$B$581="Marketing &amp; Publicidade",OR($B$583="rs",$B$583="pct_vgv",$B$583="pct_recebido")),AND($B$580="diretos",$B$581="Corretagem de vendas",OR($B$583="pct_vgv")),AND($B$580="diretos",$B$581="Projetos",OR($B$583="rs",$B$583="rs_m2_priv",$B$583="pct_constr")),AND($B$580="diretos",$B$581="Licenças e Aprovações",OR($B$583="rs",$B$583="rs_m2_priv")),AND($B$580="diretos",$B$581="Manutenção pós-obra",OR($B$583="rs",$B$583="pct_vgv",$B$583="pct_recebido")),AND($B$580="diretos",$B$581="Outro",OR($B$583="rs",$B$583="pct_vgv",$B$583="pct_recebido")),AND($B$580="indireto",$B$581="Marketing global",OR($B$583="rs",$B$583="pct_vgv",$B$583="pct_recebido")),AND($B$580="indireto",$B$581="Stand de vendas",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="indireto",$B$581="Gestão",OR($B$583="rs",$B$583="pct_vgv",$B$583="pct_recebido")),AND($B$580="indireto",$B$581="Outro",OR($B$583="rs",$B$583="pct_vgv",$B$583="pct_recebido")),AND($B$580="financeiro",$B$581="Juros de financiamento",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="financeiro",$B$581="Taxas bancárias",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="financeiro",$B$581="Estruturação de dívida",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="financeiro",$B$581="Investidores",OR($B$583="rs",$B$583="pct_vgv")),AND($B$580="financeiro",$B$581="Outro",OR($B$583="rs",$B$583="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$584&lt;&gt;"",$B$585&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$583,3)="pct",$B$585="",$B$584=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C898" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D898" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="19" t="inlineStr">
+        <is>
+          <t>Custo 25 — conferência</t>
+        </is>
+      </c>
+      <c r="B899" s="24">
+        <f>IF(AND($B$591="",$B$592=""),"",IF(OR($B$591="",$B$592="",$B$594=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$591="terreno",$B$592="Preço",OR($B$594="rs",$B$594="rs_m2_terreno")),AND($B$591="terreno",$B$592="Registro",OR($B$594="rs",$B$594="rs_m2_priv")),AND($B$591="terreno",$B$592="Outro",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="obra",$B$592="Construção",OR($B$594="rs",$B$594="rs_m2_priv")),AND($B$591="obra",$B$592="Outorga",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="obra",$B$592="Decoração",OR($B$594="rs",$B$594="rs_m2_priv")),AND($B$591="obra",$B$592="Gestão da obra",OR($B$594="rs",$B$594="pct_obra")),AND($B$591="obra",$B$592="Contingência",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="obra",$B$592="Outro",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="diretos",$B$592="Marketing &amp; Publicidade",OR($B$594="rs",$B$594="pct_vgv",$B$594="pct_recebido")),AND($B$591="diretos",$B$592="Corretagem de vendas",OR($B$594="pct_vgv")),AND($B$591="diretos",$B$592="Projetos",OR($B$594="rs",$B$594="rs_m2_priv",$B$594="pct_constr")),AND($B$591="diretos",$B$592="Licenças e Aprovações",OR($B$594="rs",$B$594="rs_m2_priv")),AND($B$591="diretos",$B$592="Manutenção pós-obra",OR($B$594="rs",$B$594="pct_vgv",$B$594="pct_recebido")),AND($B$591="diretos",$B$592="Outro",OR($B$594="rs",$B$594="pct_vgv",$B$594="pct_recebido")),AND($B$591="indireto",$B$592="Marketing global",OR($B$594="rs",$B$594="pct_vgv",$B$594="pct_recebido")),AND($B$591="indireto",$B$592="Stand de vendas",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="indireto",$B$592="Gestão",OR($B$594="rs",$B$594="pct_vgv",$B$594="pct_recebido")),AND($B$591="indireto",$B$592="Outro",OR($B$594="rs",$B$594="pct_vgv",$B$594="pct_recebido")),AND($B$591="financeiro",$B$592="Juros de financiamento",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="financeiro",$B$592="Taxas bancárias",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="financeiro",$B$592="Estruturação de dívida",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="financeiro",$B$592="Investidores",OR($B$594="rs",$B$594="pct_vgv")),AND($B$591="financeiro",$B$592="Outro",OR($B$594="rs",$B$594="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$595&lt;&gt;"",$B$596&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$594,3)="pct",$B$596="",$B$595=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C899" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D899" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="19" t="inlineStr">
+        <is>
+          <t>Custo 26 — conferência</t>
+        </is>
+      </c>
+      <c r="B900" s="24">
+        <f>IF(AND($B$602="",$B$603=""),"",IF(OR($B$602="",$B$603="",$B$605=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$602="terreno",$B$603="Preço",OR($B$605="rs",$B$605="rs_m2_terreno")),AND($B$602="terreno",$B$603="Registro",OR($B$605="rs",$B$605="rs_m2_priv")),AND($B$602="terreno",$B$603="Outro",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="obra",$B$603="Construção",OR($B$605="rs",$B$605="rs_m2_priv")),AND($B$602="obra",$B$603="Outorga",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="obra",$B$603="Decoração",OR($B$605="rs",$B$605="rs_m2_priv")),AND($B$602="obra",$B$603="Gestão da obra",OR($B$605="rs",$B$605="pct_obra")),AND($B$602="obra",$B$603="Contingência",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="obra",$B$603="Outro",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="diretos",$B$603="Marketing &amp; Publicidade",OR($B$605="rs",$B$605="pct_vgv",$B$605="pct_recebido")),AND($B$602="diretos",$B$603="Corretagem de vendas",OR($B$605="pct_vgv")),AND($B$602="diretos",$B$603="Projetos",OR($B$605="rs",$B$605="rs_m2_priv",$B$605="pct_constr")),AND($B$602="diretos",$B$603="Licenças e Aprovações",OR($B$605="rs",$B$605="rs_m2_priv")),AND($B$602="diretos",$B$603="Manutenção pós-obra",OR($B$605="rs",$B$605="pct_vgv",$B$605="pct_recebido")),AND($B$602="diretos",$B$603="Outro",OR($B$605="rs",$B$605="pct_vgv",$B$605="pct_recebido")),AND($B$602="indireto",$B$603="Marketing global",OR($B$605="rs",$B$605="pct_vgv",$B$605="pct_recebido")),AND($B$602="indireto",$B$603="Stand de vendas",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="indireto",$B$603="Gestão",OR($B$605="rs",$B$605="pct_vgv",$B$605="pct_recebido")),AND($B$602="indireto",$B$603="Outro",OR($B$605="rs",$B$605="pct_vgv",$B$605="pct_recebido")),AND($B$602="financeiro",$B$603="Juros de financiamento",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="financeiro",$B$603="Taxas bancárias",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="financeiro",$B$603="Estruturação de dívida",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="financeiro",$B$603="Investidores",OR($B$605="rs",$B$605="pct_vgv")),AND($B$602="financeiro",$B$603="Outro",OR($B$605="rs",$B$605="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$606&lt;&gt;"",$B$607&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$605,3)="pct",$B$607="",$B$606=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C900" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D900" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="19" t="inlineStr">
+        <is>
+          <t>Custo 27 — conferência</t>
+        </is>
+      </c>
+      <c r="B901" s="24">
+        <f>IF(AND($B$613="",$B$614=""),"",IF(OR($B$613="",$B$614="",$B$616=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$613="terreno",$B$614="Preço",OR($B$616="rs",$B$616="rs_m2_terreno")),AND($B$613="terreno",$B$614="Registro",OR($B$616="rs",$B$616="rs_m2_priv")),AND($B$613="terreno",$B$614="Outro",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="obra",$B$614="Construção",OR($B$616="rs",$B$616="rs_m2_priv")),AND($B$613="obra",$B$614="Outorga",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="obra",$B$614="Decoração",OR($B$616="rs",$B$616="rs_m2_priv")),AND($B$613="obra",$B$614="Gestão da obra",OR($B$616="rs",$B$616="pct_obra")),AND($B$613="obra",$B$614="Contingência",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="obra",$B$614="Outro",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="diretos",$B$614="Marketing &amp; Publicidade",OR($B$616="rs",$B$616="pct_vgv",$B$616="pct_recebido")),AND($B$613="diretos",$B$614="Corretagem de vendas",OR($B$616="pct_vgv")),AND($B$613="diretos",$B$614="Projetos",OR($B$616="rs",$B$616="rs_m2_priv",$B$616="pct_constr")),AND($B$613="diretos",$B$614="Licenças e Aprovações",OR($B$616="rs",$B$616="rs_m2_priv")),AND($B$613="diretos",$B$614="Manutenção pós-obra",OR($B$616="rs",$B$616="pct_vgv",$B$616="pct_recebido")),AND($B$613="diretos",$B$614="Outro",OR($B$616="rs",$B$616="pct_vgv",$B$616="pct_recebido")),AND($B$613="indireto",$B$614="Marketing global",OR($B$616="rs",$B$616="pct_vgv",$B$616="pct_recebido")),AND($B$613="indireto",$B$614="Stand de vendas",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="indireto",$B$614="Gestão",OR($B$616="rs",$B$616="pct_vgv",$B$616="pct_recebido")),AND($B$613="indireto",$B$614="Outro",OR($B$616="rs",$B$616="pct_vgv",$B$616="pct_recebido")),AND($B$613="financeiro",$B$614="Juros de financiamento",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="financeiro",$B$614="Taxas bancárias",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="financeiro",$B$614="Estruturação de dívida",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="financeiro",$B$614="Investidores",OR($B$616="rs",$B$616="pct_vgv")),AND($B$613="financeiro",$B$614="Outro",OR($B$616="rs",$B$616="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$617&lt;&gt;"",$B$618&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$616,3)="pct",$B$618="",$B$617=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C901" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D901" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="19" t="inlineStr">
+        <is>
+          <t>Custo 28 — conferência</t>
+        </is>
+      </c>
+      <c r="B902" s="24">
+        <f>IF(AND($B$624="",$B$625=""),"",IF(OR($B$624="",$B$625="",$B$627=""),"⚠ falta grupo, categoria ou unidade",IF(NOT(OR(AND($B$624="terreno",$B$625="Preço",OR($B$627="rs",$B$627="rs_m2_terreno")),AND($B$624="terreno",$B$625="Registro",OR($B$627="rs",$B$627="rs_m2_priv")),AND($B$624="terreno",$B$625="Outro",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="obra",$B$625="Construção",OR($B$627="rs",$B$627="rs_m2_priv")),AND($B$624="obra",$B$625="Outorga",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="obra",$B$625="Decoração",OR($B$627="rs",$B$627="rs_m2_priv")),AND($B$624="obra",$B$625="Gestão da obra",OR($B$627="rs",$B$627="pct_obra")),AND($B$624="obra",$B$625="Contingência",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="obra",$B$625="Outro",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="diretos",$B$625="Marketing &amp; Publicidade",OR($B$627="rs",$B$627="pct_vgv",$B$627="pct_recebido")),AND($B$624="diretos",$B$625="Corretagem de vendas",OR($B$627="pct_vgv")),AND($B$624="diretos",$B$625="Projetos",OR($B$627="rs",$B$627="rs_m2_priv",$B$627="pct_constr")),AND($B$624="diretos",$B$625="Licenças e Aprovações",OR($B$627="rs",$B$627="rs_m2_priv")),AND($B$624="diretos",$B$625="Manutenção pós-obra",OR($B$627="rs",$B$627="pct_vgv",$B$627="pct_recebido")),AND($B$624="diretos",$B$625="Outro",OR($B$627="rs",$B$627="pct_vgv",$B$627="pct_recebido")),AND($B$624="indireto",$B$625="Marketing global",OR($B$627="rs",$B$627="pct_vgv",$B$627="pct_recebido")),AND($B$624="indireto",$B$625="Stand de vendas",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="indireto",$B$625="Gestão",OR($B$627="rs",$B$627="pct_vgv",$B$627="pct_recebido")),AND($B$624="indireto",$B$625="Outro",OR($B$627="rs",$B$627="pct_vgv",$B$627="pct_recebido")),AND($B$624="financeiro",$B$625="Juros de financiamento",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="financeiro",$B$625="Taxas bancárias",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="financeiro",$B$625="Estruturação de dívida",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="financeiro",$B$625="Investidores",OR($B$627="rs",$B$627="pct_vgv")),AND($B$624="financeiro",$B$625="Outro",OR($B$627="rs",$B$627="pct_vgv")))),"⚠ unidade não aceita nesta categoria",IF(AND($B$628&lt;&gt;"",$B$629&lt;&gt;""),"⚠ preencha só uma linha de valor",IF(IF(LEFT($B$627,3)="pct",$B$629="",$B$628=""),"⚠ falta o valor na linha certa","OK")))))</f>
+        <v/>
+      </c>
+      <c r="C902" s="21" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="D902" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="19" t="inlineStr">
+        <is>
+          <t>Cada 1% do VGV de tabela equivale a (para converter Projetos, que não aceita % do VGV)</t>
+        </is>
+      </c>
+      <c r="B903" s="25">
+        <f>$B$788*0.01</f>
+        <v/>
+      </c>
+      <c r="C903" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D903" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="19" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — terreno</t>
+        </is>
+      </c>
+      <c r="B904" s="25">
+        <f>IF($B$327="terreno",N($B$847),0)+IF($B$338="terreno",N($B$848),0)+IF($B$349="terreno",N($B$849),0)+IF($B$360="terreno",N($B$850),0)+IF($B$371="terreno",N($B$851),0)+IF($B$382="terreno",N($B$852),0)+IF($B$393="terreno",N($B$853),0)+IF($B$404="terreno",N($B$854),0)+IF($B$415="terreno",N($B$855),0)+IF($B$426="terreno",N($B$856),0)+IF($B$437="terreno",N($B$857),0)+IF($B$448="terreno",N($B$858),0)+IF($B$459="terreno",N($B$859),0)+IF($B$470="terreno",N($B$860),0)+IF($B$481="terreno",N($B$861),0)+IF($B$492="terreno",N($B$862),0)+IF($B$503="terreno",N($B$863),0)+IF($B$514="terreno",N($B$864),0)+IF($B$525="terreno",N($B$865),0)+IF($B$536="terreno",N($B$866),0)+IF($B$547="terreno",N($B$867),0)+IF($B$558="terreno",N($B$868),0)+IF($B$569="terreno",N($B$869),0)+IF($B$580="terreno",N($B$870),0)+IF($B$591="terreno",N($B$871),0)+IF($B$602="terreno",N($B$872),0)+IF($B$613="terreno",N($B$873),0)+IF($B$624="terreno",N($B$874),0)</f>
+        <v/>
+      </c>
+      <c r="C904" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D904" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="19" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — obra</t>
+        </is>
+      </c>
+      <c r="B905" s="25">
+        <f>IF($B$327="obra",N($B$847),0)+IF($B$338="obra",N($B$848),0)+IF($B$349="obra",N($B$849),0)+IF($B$360="obra",N($B$850),0)+IF($B$371="obra",N($B$851),0)+IF($B$382="obra",N($B$852),0)+IF($B$393="obra",N($B$853),0)+IF($B$404="obra",N($B$854),0)+IF($B$415="obra",N($B$855),0)+IF($B$426="obra",N($B$856),0)+IF($B$437="obra",N($B$857),0)+IF($B$448="obra",N($B$858),0)+IF($B$459="obra",N($B$859),0)+IF($B$470="obra",N($B$860),0)+IF($B$481="obra",N($B$861),0)+IF($B$492="obra",N($B$862),0)+IF($B$503="obra",N($B$863),0)+IF($B$514="obra",N($B$864),0)+IF($B$525="obra",N($B$865),0)+IF($B$536="obra",N($B$866),0)+IF($B$547="obra",N($B$867),0)+IF($B$558="obra",N($B$868),0)+IF($B$569="obra",N($B$869),0)+IF($B$580="obra",N($B$870),0)+IF($B$591="obra",N($B$871),0)+IF($B$602="obra",N($B$872),0)+IF($B$613="obra",N($B$873),0)+IF($B$624="obra",N($B$874),0)</f>
+        <v/>
+      </c>
+      <c r="C905" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D905" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="19" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — diretos</t>
+        </is>
+      </c>
+      <c r="B906" s="25">
+        <f>IF($B$327="diretos",N($B$847),0)+IF($B$338="diretos",N($B$848),0)+IF($B$349="diretos",N($B$849),0)+IF($B$360="diretos",N($B$850),0)+IF($B$371="diretos",N($B$851),0)+IF($B$382="diretos",N($B$852),0)+IF($B$393="diretos",N($B$853),0)+IF($B$404="diretos",N($B$854),0)+IF($B$415="diretos",N($B$855),0)+IF($B$426="diretos",N($B$856),0)+IF($B$437="diretos",N($B$857),0)+IF($B$448="diretos",N($B$858),0)+IF($B$459="diretos",N($B$859),0)+IF($B$470="diretos",N($B$860),0)+IF($B$481="diretos",N($B$861),0)+IF($B$492="diretos",N($B$862),0)+IF($B$503="diretos",N($B$863),0)+IF($B$514="diretos",N($B$864),0)+IF($B$525="diretos",N($B$865),0)+IF($B$536="diretos",N($B$866),0)+IF($B$547="diretos",N($B$867),0)+IF($B$558="diretos",N($B$868),0)+IF($B$569="diretos",N($B$869),0)+IF($B$580="diretos",N($B$870),0)+IF($B$591="diretos",N($B$871),0)+IF($B$602="diretos",N($B$872),0)+IF($B$613="diretos",N($B$873),0)+IF($B$624="diretos",N($B$874),0)</f>
+        <v/>
+      </c>
+      <c r="C906" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D906" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="19" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — indireto</t>
+        </is>
+      </c>
+      <c r="B907" s="25">
+        <f>IF($B$327="indireto",N($B$847),0)+IF($B$338="indireto",N($B$848),0)+IF($B$349="indireto",N($B$849),0)+IF($B$360="indireto",N($B$850),0)+IF($B$371="indireto",N($B$851),0)+IF($B$382="indireto",N($B$852),0)+IF($B$393="indireto",N($B$853),0)+IF($B$404="indireto",N($B$854),0)+IF($B$415="indireto",N($B$855),0)+IF($B$426="indireto",N($B$856),0)+IF($B$437="indireto",N($B$857),0)+IF($B$448="indireto",N($B$858),0)+IF($B$459="indireto",N($B$859),0)+IF($B$470="indireto",N($B$860),0)+IF($B$481="indireto",N($B$861),0)+IF($B$492="indireto",N($B$862),0)+IF($B$503="indireto",N($B$863),0)+IF($B$514="indireto",N($B$864),0)+IF($B$525="indireto",N($B$865),0)+IF($B$536="indireto",N($B$866),0)+IF($B$547="indireto",N($B$867),0)+IF($B$558="indireto",N($B$868),0)+IF($B$569="indireto",N($B$869),0)+IF($B$580="indireto",N($B$870),0)+IF($B$591="indireto",N($B$871),0)+IF($B$602="indireto",N($B$872),0)+IF($B$613="indireto",N($B$873),0)+IF($B$624="indireto",N($B$874),0)</f>
+        <v/>
+      </c>
+      <c r="C907" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D907" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="19" t="inlineStr">
+        <is>
+          <t>Σ custos conversíveis — financeiro</t>
+        </is>
+      </c>
+      <c r="B908" s="25">
+        <f>IF($B$327="financeiro",N($B$847),0)+IF($B$338="financeiro",N($B$848),0)+IF($B$349="financeiro",N($B$849),0)+IF($B$360="financeiro",N($B$850),0)+IF($B$371="financeiro",N($B$851),0)+IF($B$382="financeiro",N($B$852),0)+IF($B$393="financeiro",N($B$853),0)+IF($B$404="financeiro",N($B$854),0)+IF($B$415="financeiro",N($B$855),0)+IF($B$426="financeiro",N($B$856),0)+IF($B$437="financeiro",N($B$857),0)+IF($B$448="financeiro",N($B$858),0)+IF($B$459="financeiro",N($B$859),0)+IF($B$470="financeiro",N($B$860),0)+IF($B$481="financeiro",N($B$861),0)+IF($B$492="financeiro",N($B$862),0)+IF($B$503="financeiro",N($B$863),0)+IF($B$514="financeiro",N($B$864),0)+IF($B$525="financeiro",N($B$865),0)+IF($B$536="financeiro",N($B$866),0)+IF($B$547="financeiro",N($B$867),0)+IF($B$558="financeiro",N($B$868),0)+IF($B$569="financeiro",N($B$869),0)+IF($B$580="financeiro",N($B$870),0)+IF($B$591="financeiro",N($B$871),0)+IF($B$602="financeiro",N($B$872),0)+IF($B$613="financeiro",N($B$873),0)+IF($B$624="financeiro",N($B$874),0)</f>
+        <v/>
+      </c>
+      <c r="C908" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D908" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="19" t="inlineStr">
+        <is>
+          <t>Permuta física 1 — VGV entregue (unidades × área × preço sugerido)</t>
+        </is>
+      </c>
+      <c r="B909" s="25">
+        <f>IF($B$635="",0,N($B$636)*(($B$59=$B$635)*(N($B$61)+N($B$62))*N($B$66)+($B$68=$B$635)*(N($B$70)+N($B$71))*N($B$75)+($B$77=$B$635)*(N($B$79)+N($B$80))*N($B$84)+($B$86=$B$635)*(N($B$88)+N($B$89))*N($B$93)+($B$95=$B$635)*(N($B$97)+N($B$98))*N($B$102)+($B$104=$B$635)*(N($B$106)+N($B$107))*N($B$111)+($B$113=$B$635)*(N($B$115)+N($B$116))*N($B$120)+($B$122=$B$635)*(N($B$124)+N($B$125))*N($B$129)+($B$131=$B$635)*(N($B$133)+N($B$134))*N($B$138)+($B$140=$B$635)*(N($B$142)+N($B$143))*N($B$147)))</f>
+        <v/>
+      </c>
+      <c r="C909" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D909" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="19" t="inlineStr">
+        <is>
+          <t>Permuta financeira 1 — equivalente em R$</t>
+        </is>
+      </c>
+      <c r="B910" s="25">
+        <f>IF($B$640="pct_vgv",N($B$642)*$B$788,IF($B$640="rs",N($B$641),0))</f>
+        <v/>
+      </c>
+      <c r="C910" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D910" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="19" t="inlineStr">
+        <is>
+          <t>Permuta física 2 — VGV entregue (unidades × área × preço sugerido)</t>
+        </is>
+      </c>
+      <c r="B911" s="25">
+        <f>IF($B$637="",0,N($B$638)*(($B$59=$B$637)*(N($B$61)+N($B$62))*N($B$66)+($B$68=$B$637)*(N($B$70)+N($B$71))*N($B$75)+($B$77=$B$637)*(N($B$79)+N($B$80))*N($B$84)+($B$86=$B$637)*(N($B$88)+N($B$89))*N($B$93)+($B$95=$B$637)*(N($B$97)+N($B$98))*N($B$102)+($B$104=$B$637)*(N($B$106)+N($B$107))*N($B$111)+($B$113=$B$637)*(N($B$115)+N($B$116))*N($B$120)+($B$122=$B$637)*(N($B$124)+N($B$125))*N($B$129)+($B$131=$B$637)*(N($B$133)+N($B$134))*N($B$138)+($B$140=$B$637)*(N($B$142)+N($B$143))*N($B$147)))</f>
+        <v/>
+      </c>
+      <c r="C911" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D911" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="19" t="inlineStr">
+        <is>
+          <t>Permuta financeira 2 — equivalente em R$</t>
+        </is>
+      </c>
+      <c r="B912" s="25">
+        <f>IF($B$645="pct_vgv",N($B$647)*$B$788,IF($B$645="rs",N($B$646),0))</f>
+        <v/>
+      </c>
+      <c r="C912" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D912" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="19" t="inlineStr">
+        <is>
+          <t>Σ valor das dívidas</t>
+        </is>
+      </c>
+      <c r="B913" s="25">
+        <f>N($B$662)+N($B$675)+N($B$688)</f>
+        <v/>
+      </c>
+      <c r="C913" s="21" t="inlineStr">
+        <is>
+          <t>R$</t>
+        </is>
+      </c>
+      <c r="D913" s="22" t="inlineStr">
+        <is>
+          <t>calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="19" t="inlineStr">
+        <is>
           <t>Σ valor dos equities</t>
         </is>
       </c>
-      <c r="B885" s="25">
+      <c r="B914" s="25">
         <f>N($B$701)+N($B$708)+N($B$715)</f>
         <v/>
       </c>
-      <c r="C885" s="21" t="inlineStr">
+      <c r="C914" s="21" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D885" s="22" t="inlineStr">
+      <c r="D914" s="22" t="inlineStr">
         <is>
           <t>calculado</t>
         </is>
       </c>
     </row>
-    <row r="888">
-      <c r="F888" t="inlineStr">
+    <row r="917">
+      <c r="F917" t="inlineStr">
         <is>
           <t>Preço</t>
         </is>
       </c>
     </row>
-    <row r="889">
-      <c r="F889" t="inlineStr">
+    <row r="918">
+      <c r="F918" t="inlineStr">
         <is>
           <t>Registro</t>
         </is>
       </c>
     </row>
-    <row r="890">
-      <c r="F890" t="inlineStr">
+    <row r="919">
+      <c r="F919" t="inlineStr">
         <is>
           <t>Outro</t>
         </is>
       </c>
     </row>
-    <row r="891">
-      <c r="F891" t="inlineStr">
+    <row r="920">
+      <c r="F920" t="inlineStr">
         <is>
           <t>Construção</t>
         </is>
       </c>
     </row>
-    <row r="892">
-      <c r="F892" t="inlineStr">
+    <row r="921">
+      <c r="F921" t="inlineStr">
         <is>
           <t>Outorga</t>
         </is>
       </c>
     </row>
-    <row r="893">
-      <c r="F893" t="inlineStr">
+    <row r="922">
+      <c r="F922" t="inlineStr">
         <is>
           <t>Decoração</t>
         </is>
       </c>
     </row>
-    <row r="894">
-      <c r="F894" t="inlineStr">
+    <row r="923">
+      <c r="F923" t="inlineStr">
         <is>
           <t>Gestão da obra</t>
         </is>
       </c>
     </row>
-    <row r="895">
-      <c r="F895" t="inlineStr">
+    <row r="924">
+      <c r="F924" t="inlineStr">
         <is>
           <t>Contingência</t>
         </is>
       </c>
     </row>
-    <row r="896">
-      <c r="F896" t="inlineStr">
+    <row r="925">
+      <c r="F925" t="inlineStr">
         <is>
           <t>Marketing &amp; Publicidade</t>
         </is>
       </c>
     </row>
-    <row r="897">
-      <c r="F897" t="inlineStr">
+    <row r="926">
+      <c r="F926" t="inlineStr">
         <is>
           <t>Corretagem de vendas</t>
         </is>
       </c>
     </row>
-    <row r="898">
-      <c r="F898" t="inlineStr">
+    <row r="927">
+      <c r="F927" t="inlineStr">
         <is>
           <t>Projetos</t>
         </is>
       </c>
     </row>
-    <row r="899">
-      <c r="F899" t="inlineStr">
+    <row r="928">
+      <c r="F928" t="inlineStr">
         <is>
           <t>Licenças e Aprovações</t>
         </is>
       </c>
     </row>
-    <row r="900">
-      <c r="F900" t="inlineStr">
+    <row r="929">
+      <c r="F929" t="inlineStr">
         <is>
           <t>Manutenção pós-obra</t>
         </is>
       </c>
     </row>
-    <row r="901">
-      <c r="F901" t="inlineStr">
+    <row r="930">
+      <c r="F930" t="inlineStr">
         <is>
           <t>Marketing global</t>
         </is>
       </c>
     </row>
-    <row r="902">
-      <c r="F902" t="inlineStr">
+    <row r="931">
+      <c r="F931" t="inlineStr">
         <is>
           <t>Gestão</t>
         </is>
       </c>
     </row>
-    <row r="903">
-      <c r="F903" t="inlineStr">
+    <row r="932">
+      <c r="F932" t="inlineStr">
         <is>
           <t>Stand de vendas</t>
         </is>
       </c>
     </row>
-    <row r="904">
-      <c r="F904" t="inlineStr">
+    <row r="933">
+      <c r="F933" t="inlineStr">
         <is>
           <t>Juros de financiamento</t>
         </is>
       </c>
     </row>
-    <row r="905">
-      <c r="F905" t="inlineStr">
+    <row r="934">
+      <c r="F934" t="inlineStr">
         <is>
           <t>Taxas bancárias</t>
         </is>
       </c>
     </row>
-    <row r="906">
-      <c r="F906" t="inlineStr">
+    <row r="935">
+      <c r="F935" t="inlineStr">
         <is>
           <t>Estruturação de dívida</t>
         </is>
       </c>
     </row>
-    <row r="907">
-      <c r="F907" t="inlineStr">
+    <row r="936">
+      <c r="F936" t="inlineStr">
         <is>
           <t>Investidores</t>
         </is>
       </c>
     </row>
-    <row r="909">
-      <c r="F909" t="inlineStr">
+    <row r="938">
+      <c r="F938" t="inlineStr">
         <is>
           <t>planejamento</t>
         </is>
       </c>
     </row>
-    <row r="910">
-      <c r="F910" t="inlineStr">
+    <row r="939">
+      <c r="F939" t="inlineStr">
         <is>
           <t>pre_lancamento</t>
         </is>
       </c>
     </row>
-    <row r="911">
-      <c r="F911" t="inlineStr">
+    <row r="940">
+      <c r="F940" t="inlineStr">
         <is>
           <t>lancamento</t>
         </is>
       </c>
     </row>
-    <row r="912">
-      <c r="F912" t="inlineStr">
+    <row r="941">
+      <c r="F941" t="inlineStr">
         <is>
           <t>obra</t>
         </is>
       </c>
     </row>
-    <row r="913">
-      <c r="F913" t="inlineStr">
+    <row r="942">
+      <c r="F942" t="inlineStr">
         <is>
           <t>pos_obra</t>
         </is>
       </c>
     </row>
-    <row r="914">
-      <c r="F914" t="inlineStr">
+    <row r="943">
+      <c r="F943" t="inlineStr">
         <is>
           <t>customizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Linear</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Curva S</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>unit_delivery</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>sales_revenue</t>
         </is>
       </c>
     </row>
@@ -16823,7 +17460,7 @@
     <mergeCell ref="A158:D158"/>
     <mergeCell ref="A651:D651"/>
   </mergeCells>
-  <dataValidations count="23">
+  <dataValidations count="24">
     <dataValidation sqref="B5 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="No máximo 200 caracteres." type="textLength" errorStyle="warning" operator="lessThanOrEqual">
       <formula1>200</formula1>
     </dataValidation>
@@ -16882,14 +17519,17 @@
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
+    <dataValidation sqref="B333 B344 B355 B366 B377 B388 B399 B410 B421 B432 B443 B454 B465 B476 B487 B498 B509 B520 B531 B542 B553 B564 B575 B586 B597 B608 B619 B630" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
+      <formula1>$F$945:$F$948</formula1>
+    </dataValidation>
     <dataValidation sqref="B334 B345 B356 B367 B378 B389 B400 B411 B422 B433 B444 B455 B466 B477 B488 B499 B510 B521 B532 B543 B554 B565 B576 B587 B598 B609 B620 B631 B663 B676 B689 B702 B709 B716" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
-      <formula1>$F$909:$F$914</formula1>
+      <formula1>$F$938:$F$943</formula1>
     </dataValidation>
     <dataValidation sqref="B360 B371 B382 B393 B404 B415 B426 B437 B448 B459 B470 B481 B492 B503 B514 B525 B536 B547 B558 B569 B580 B591 B602 B613 B624" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"terreno,obra,diretos,indireto,financeiro"</formula1>
     </dataValidation>
     <dataValidation sqref="B361 B372 B383 B394 B405 B416 B427 B438 B449 B460 B471 B482 B493 B504 B515 B526 B537 B548 B559 B570 B581 B592 B603 B614 B625" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da lista de referência — confirme." type="list" errorStyle="warning">
-      <formula1>$F$888:$F$907</formula1>
+      <formula1>$F$917:$F$936</formula1>
     </dataValidation>
     <dataValidation sqref="B640 B645" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"rs,pct_vgv"</formula1>

--- a/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>lista: manual (inserir novo) | nucleo (buscar terreno)</t>
+          <t>lista: manual (inserir novo) | nucleo (buscar terreno — o importador só aceita manual)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -6216,7 +6216,7 @@
     <row r="324" ht="117" customHeight="1">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>Categorias e unidades aceitas (rs = R$ · rs_m2_priv = R$/m² privativo · rs_m2_terreno · pct_vgv · pct_receita · pct_obra · pct_recebido · pct_constr). TERRENO: Preço (rs, rs_m2_terreno; permuta financeira: rs, pct_vgv) · Registro (rs, rs_m2_priv) · Outro (rs, pct_vgv). OBRA: Construção, Decoração (rs, rs_m2_priv) · Outorga, Contingência, Outro (rs, pct_vgv) · Gestão da obra (rs, pct_obra). DIRETOS: Marketing &amp; Publicidade, Manutenção pós-obra, Outro (rs, pct_vgv, pct_recebido) · Corretagem de vendas (pct_vgv) · Projetos (rs, rs_m2_priv, pct_constr) · Licenças e Aprovações (rs, rs_m2_priv). INDIRETO: Marketing global, Gestão, Outro (rs, pct_vgv, pct_recebido) · Stand de vendas (rs, pct_vgv). FINANCEIRO: Juros de financiamento, Taxas bancárias, Estruturação de dívida, Investidores, Outro (rs, pct_vgv). Cronograma padrão: terreno/Preço = customizado; terreno/demais, indireto = planejamento; obra/diretos/financeiro = obra; Manutenção pós-obra = pos_obra. Início e Duração só valem com cronograma = customizado; cronograma ancorado em fase customizada = escrever "fase: &lt;nome da fase&gt;". Corretagem sai no mês da venda e a permuta física na entrega das unidades (não escolhem distribuição). Obrigatórias: terreno/Preço, obra/Construção, diretos/Corretagem de vendas (% VGV).</t>
+          <t>Categorias e unidades aceitas (rs = R$ · rs_m2_priv = R$/m² privativo · rs_m2_terreno · pct_vgv · pct_obra · pct_recebido · pct_constr). TERRENO: Preço (rs, rs_m2_terreno; permuta financeira: rs, pct_vgv) · Registro (rs, rs_m2_priv) · Outro (rs, pct_vgv). OBRA: Construção, Decoração (rs, rs_m2_priv) · Outorga, Contingência, Outro (rs, pct_vgv) · Gestão da obra (rs, pct_obra). DIRETOS: Marketing &amp; Publicidade, Manutenção pós-obra, Outro (rs, pct_vgv, pct_recebido) · Corretagem de vendas (pct_vgv) · Projetos (rs, rs_m2_priv, pct_constr) · Licenças e Aprovações (rs, rs_m2_priv). INDIRETO: Marketing global, Gestão, Outro (rs, pct_vgv, pct_recebido) · Stand de vendas (rs, pct_vgv). FINANCEIRO: Juros de financiamento, Taxas bancárias, Estruturação de dívida, Investidores, Outro (rs, pct_vgv). Cronograma padrão: terreno/Preço = customizado; terreno/demais, indireto = planejamento; obra/diretos/financeiro = obra; Manutenção pós-obra = pos_obra. Início e Duração só valem com cronograma = customizado; cronograma ancorado em fase customizada = escrever "fase: &lt;nome da fase&gt;". Corretagem sai no mês da venda e a permuta física na entrega das unidades (não escolhem distribuição). Obrigatórias: terreno/Preço, obra/Construção, diretos/Corretagem de vendas (% VGV).</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D330" s="8" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D341" s="8" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D352" s="8" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D363" s="8" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C374" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D374" s="8" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D385" s="8" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="C396" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D396" s="8" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="C407" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D407" s="8" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="C418" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D418" s="8" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="C429" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D429" s="8" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="C440" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D440" s="8" t="inlineStr">
@@ -8590,7 +8590,7 @@
       <c r="B451" s="6" t="n"/>
       <c r="C451" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D451" s="8" t="inlineStr">
@@ -8775,7 +8775,7 @@
       <c r="B462" s="6" t="n"/>
       <c r="C462" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D462" s="8" t="inlineStr">
@@ -8960,7 +8960,7 @@
       <c r="B473" s="6" t="n"/>
       <c r="C473" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D473" s="8" t="inlineStr">
@@ -9145,7 +9145,7 @@
       <c r="B484" s="6" t="n"/>
       <c r="C484" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D484" s="8" t="inlineStr">
@@ -9330,7 +9330,7 @@
       <c r="B495" s="6" t="n"/>
       <c r="C495" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D495" s="8" t="inlineStr">
@@ -9515,7 +9515,7 @@
       <c r="B506" s="6" t="n"/>
       <c r="C506" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D506" s="8" t="inlineStr">
@@ -9700,7 +9700,7 @@
       <c r="B517" s="6" t="n"/>
       <c r="C517" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D517" s="8" t="inlineStr">
@@ -9885,7 +9885,7 @@
       <c r="B528" s="6" t="n"/>
       <c r="C528" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D528" s="8" t="inlineStr">
@@ -10070,7 +10070,7 @@
       <c r="B539" s="6" t="n"/>
       <c r="C539" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D539" s="8" t="inlineStr">
@@ -10255,7 +10255,7 @@
       <c r="B550" s="6" t="n"/>
       <c r="C550" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D550" s="8" t="inlineStr">
@@ -10440,7 +10440,7 @@
       <c r="B561" s="6" t="n"/>
       <c r="C561" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D561" s="8" t="inlineStr">
@@ -10625,7 +10625,7 @@
       <c r="B572" s="6" t="n"/>
       <c r="C572" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D572" s="8" t="inlineStr">
@@ -10810,7 +10810,7 @@
       <c r="B583" s="6" t="n"/>
       <c r="C583" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D583" s="8" t="inlineStr">
@@ -10995,7 +10995,7 @@
       <c r="B594" s="6" t="n"/>
       <c r="C594" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D594" s="8" t="inlineStr">
@@ -11180,7 +11180,7 @@
       <c r="B605" s="6" t="n"/>
       <c r="C605" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D605" s="8" t="inlineStr">
@@ -11365,7 +11365,7 @@
       <c r="B616" s="6" t="n"/>
       <c r="C616" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D616" s="8" t="inlineStr">
@@ -11550,7 +11550,7 @@
       <c r="B627" s="6" t="n"/>
       <c r="C627" s="7" t="inlineStr">
         <is>
-          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_receita | pct_obra | pct_recebido | pct_constr</t>
+          <t>lista: rs | rs_m2_priv | rs_m2_terreno | pct_vgv | pct_obra | pct_recebido | pct_constr</t>
         </is>
       </c>
       <c r="D627" s="8" t="inlineStr">
@@ -17513,7 +17513,7 @@
       <formula1>"Entrada,Parcelamento"</formula1>
     </dataValidation>
     <dataValidation sqref="B330 B341 B363 B374 B385 B396 B407 B418 B429 B440 B451 B462 B473 B484 B495 B506 B517 B528 B539 B550 B561 B572 B583 B594 B605 B616 B627" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
-      <formula1>"rs,rs_m2_priv,rs_m2_terreno,pct_vgv,pct_receita,pct_obra,pct_recebido,pct_constr"</formula1>
+      <formula1>"rs,rs_m2_priv,rs_m2_terreno,pct_vgv,pct_obra,pct_recebido,pct_constr"</formula1>
     </dataValidation>
     <dataValidation sqref="B332 B343 B354 B365 B376 B387 B398 B409 B420 B431 B442 B453 B464 B475 B486 B497 B508 B519 B530 B541 B552 B563 B574 B585 B596 B607 B618 B629" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 10)." type="decimal" errorStyle="warning" operator="between">
       <formula1>0</formula1>

--- a/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
@@ -604,7 +604,7 @@
     <row r="2" ht="92" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite como porcentagem (4% ou 4 numa célula já formatada em %). O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
+          <t>Como preencher: só as células AMARELAS da coluna B. Cinza-claro com valor em negrito = fixo do tipo de estudo (não editar); cinza com itálico = calculado pelo Excel, só para conferir (não editar). * = obrigatório. PERCENTUAL: digite com o símbolo % (4%), nunca só o número. O Excel guarda 0,04; a API do app espera pontos (4) e o importador converte pelo FORMATO da célula — por isso não troque o formato das células. Números sem separador de milhar e com ponto decimal quando digitados fora do Excel. CAMPO COM VÁRIAS UNIDADES: há uma linha por unidade — preencha UMA só e deixe as outras em branco; o Excel não converte uma na outra. Listas (produtos, custos…) têm vagas numeradas; vaga totalmente em branco = sem item. Meses: 0 = mês da data de início do projeto.</t>
         </is>
       </c>
     </row>

--- a/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
+++ b/referencia/formularios/exemplos/exemplo-incorporacao-aurora-parque-avancado.xlsx
@@ -3225,7 +3225,7 @@
     <row r="150" ht="39" customHeight="1">
       <c r="A150" s="13" t="inlineStr">
         <is>
-          <t>Saldo de chaves = o Repasse acima. "Repasse bancário" é a parte dele paga pelo banco no mês seguinte ao fim da obra (vazio = 100%, tudo no banco). O resto vira carteira própria: a empresa financia o comprador em N parcelas mensais Price com os Juros de tabela, a partir do mês seguinte ao fim da obra + a carência. Loteamento sem banco: 0%.</t>
+          <t>Saldo de chaves = o Repasse acima. "Repasse bancário" é a parte dele paga pelo banco no mês seguinte ao fim da obra (vazio = 100%, tudo no banco). O resto vira carteira própria: a empresa financia o comprador em N parcelas mensais Price com os Juros de tabela, a partir do mês seguinte ao fim da obra + a carência (nunca antes do mês seguinte à venda): também a venda feita depois da entrega tem essa parte financiada. Loteamento sem banco: 0%.</t>
         </is>
       </c>
     </row>
@@ -18313,7 +18313,7 @@
     <mergeCell ref="A562:D562"/>
     <mergeCell ref="A151:D151"/>
   </mergeCells>
-  <dataValidations count="24">
+  <dataValidations count="25">
     <dataValidation sqref="B5 B14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="No máximo 200 caracteres." type="textLength" errorStyle="warning" operator="lessThanOrEqual">
       <formula1>200</formula1>
     </dataValidation>
@@ -18334,7 +18334,7 @@
       <formula1>0</formula1>
       <formula2>9.9999</formula2>
     </dataValidation>
-    <dataValidation sqref="B22 B25 B153 B154 B155 B159 B164 B165 B166 B170 B175 B176 B177 B181 B186 B187 B188 B192 B197 B198 B199 B203 B211 B213 B214 B219 B221 B222 B227 B229 B230 B235 B237 B238 B243 B245 B246 B251 B253 B254 B259 B261 B262 B267 B269 B270 B275 B277 B278 B283 B285 B286 B658 B663 B671 B672 B673 B683 B686 B696 B699 B709 B712 B721 B728 B735 B741 B742 B743 B750 B751 B752 B759 B760 B761" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 1)." type="decimal" errorStyle="warning" operator="between">
+    <dataValidation sqref="B22 B25 B153 B154 B155 B159 B164 B165 B166 B170 B175 B176 B177 B181 B186 B187 B188 B192 B197 B198 B199 B203 B211 B213 B214 B219 B221 B222 B227 B229 B230 B235 B237 B238 B243 B245 B246 B251 B253 B254 B259 B261 B262 B267 B269 B270 B275 B277 B278 B283 B285 B286 B658 B663 B671 B672 B673 B683 B686 B696 B699 B709 B712 B721 B728 B735 B742 B743 B751 B752 B760 B761" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0 a 1)." type="decimal" errorStyle="warning" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -18390,6 +18390,10 @@
     <dataValidation sqref="B720 B727 B734" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor inválido" error="Escolha um valor da lista." type="list">
       <formula1>"permuta_financeira,resultado_final"</formula1>
     </dataValidation>
+    <dataValidation sqref="B741 B750 B759" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (0.0001 a 1)." type="decimal" errorStyle="warning" operator="between">
+      <formula1>0.0001</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
     <dataValidation sqref="B766 B767 B769 B770 B772 B773 B775 B776 B778 B779" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Confira o valor" error="Valor fora da faixa esperada (-1 a 10)." type="decimal" errorStyle="warning" operator="between">
       <formula1>-1</formula1>
       <formula2>10</formula2>
